--- a/database/event/6345/event_6345_evp_summary.xlsx
+++ b/database/event/6345/event_6345_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.404</v>
+        <v>8.3971</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0151</v>
+        <v>3.0126</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9737</v>
+        <v>2.9015</v>
       </c>
       <c r="E2" t="n">
-        <v>8.404</v>
+        <v>8.3971</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8513</v>
+        <v>1.8444</v>
       </c>
       <c r="G2" t="n">
         <v>6.5527</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8513</v>
+        <v>1.8444</v>
       </c>
       <c r="I2" t="n">
         <v>1.8599</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6343</v>
+        <v>6.6249</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3802</v>
+        <v>2.3768</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2587</v>
+        <v>2.1955</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6343</v>
+        <v>6.6249</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5016</v>
+        <v>2.4922</v>
       </c>
       <c r="G3" t="n">
         <v>4.1327</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5016</v>
+        <v>2.4922</v>
       </c>
       <c r="I3" t="n">
         <v>2.5132</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3892</v>
+        <v>6.3875</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2923</v>
+        <v>2.2916</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1597</v>
+        <v>2.1009</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3892</v>
+        <v>6.3875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4566</v>
+        <v>0.4549</v>
       </c>
       <c r="G4" t="n">
         <v>5.9326</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4566</v>
+        <v>0.4549</v>
       </c>
       <c r="I4" t="n">
         <v>0.4587</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1652</v>
+        <v>6.1626</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2119</v>
+        <v>2.211</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0692</v>
+        <v>2.0113</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1652</v>
+        <v>6.1626</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6793</v>
+        <v>0.6768</v>
       </c>
       <c r="G5" t="n">
         <v>5.4858</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6793</v>
+        <v>0.6768</v>
       </c>
       <c r="I5" t="n">
         <v>0.6825</v>
@@ -686,7 +686,7 @@
         <v>1.766</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5672</v>
+        <v>1.5172</v>
       </c>
       <c r="E6" t="n">
         <v>4.9224</v>
@@ -732,7 +732,7 @@
         <v>1.2369</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9714</v>
+        <v>0.9296</v>
       </c>
       <c r="E7" t="n">
         <v>3.4475</v>
@@ -778,7 +778,7 @@
         <v>1.1352</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8569</v>
+        <v>0.8167</v>
       </c>
       <c r="E8" t="n">
         <v>3.1641</v>
@@ -824,7 +824,7 @@
         <v>0.9206</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6153</v>
+        <v>0.5784</v>
       </c>
       <c r="E9" t="n">
         <v>2.5661</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5479</v>
+        <v>2.5421</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9141</v>
+        <v>0.912</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6079</v>
+        <v>0.5689</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5479</v>
+        <v>2.5421</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5616</v>
+        <v>1.5558</v>
       </c>
       <c r="G10" t="n">
         <v>0.9863</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5616</v>
+        <v>1.5558</v>
       </c>
       <c r="I10" t="n">
         <v>1.5689</v>
@@ -916,7 +916,7 @@
         <v>0.8362000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5202</v>
+        <v>0.4846</v>
       </c>
       <c r="E11" t="n">
         <v>2.3307</v>
@@ -962,7 +962,7 @@
         <v>0.716</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3848</v>
+        <v>0.3511</v>
       </c>
       <c r="E12" t="n">
         <v>1.9956</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4889</v>
+        <v>1.4863</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5342</v>
+        <v>0.5332</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1801</v>
+        <v>0.1482</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4889</v>
+        <v>1.4863</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7109</v>
+        <v>0.7083</v>
       </c>
       <c r="G13" t="n">
         <v>0.778</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7109</v>
+        <v>0.7083</v>
       </c>
       <c r="I13" t="n">
         <v>0.7141999999999999</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0764</v>
+        <v>1.0727</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3862</v>
+        <v>0.3849</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0135</v>
+        <v>-0.0165</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0764</v>
+        <v>1.0727</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9913</v>
+        <v>0.9876</v>
       </c>
       <c r="G14" t="n">
         <v>0.0851</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9913</v>
+        <v>0.9876</v>
       </c>
       <c r="I14" t="n">
         <v>0.9959</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9696</v>
+        <v>0.9657</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3479</v>
+        <v>0.3465</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0297</v>
+        <v>-0.0592</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9696</v>
+        <v>0.9657</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0526</v>
+        <v>1.0487</v>
       </c>
       <c r="G15" t="n">
         <v>-0.083</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0526</v>
+        <v>1.0487</v>
       </c>
       <c r="I15" t="n">
         <v>1.0575</v>
@@ -1146,7 +1146,7 @@
         <v>0.3316</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0479</v>
+        <v>-0.0756</v>
       </c>
       <c r="E16" t="n">
         <v>0.9244</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9079</v>
+        <v>0.9052</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3257</v>
+        <v>0.3248</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0546</v>
+        <v>-0.0833</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9079</v>
+        <v>0.9052</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7453</v>
+        <v>0.7426</v>
       </c>
       <c r="G17" t="n">
         <v>0.1626</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7453</v>
+        <v>0.7426</v>
       </c>
       <c r="I17" t="n">
         <v>0.7488</v>
@@ -1238,7 +1238,7 @@
         <v>0.278</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1083</v>
+        <v>-0.1352</v>
       </c>
       <c r="E18" t="n">
         <v>0.7749</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7371</v>
+        <v>0.7307</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2644</v>
+        <v>0.2622</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1236</v>
+        <v>-0.1528</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7371</v>
+        <v>0.7307</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7371</v>
+        <v>1.7307</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7371</v>
+        <v>1.7307</v>
       </c>
       <c r="I19" t="n">
         <v>1.7452</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7231</v>
+        <v>0.7167</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2594</v>
+        <v>0.2571</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1292</v>
+        <v>-0.1584</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7231</v>
+        <v>0.7167</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7231</v>
+        <v>1.7167</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7231</v>
+        <v>1.7167</v>
       </c>
       <c r="I20" t="n">
         <v>1.7311</v>
@@ -1376,7 +1376,7 @@
         <v>0.2369</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1546</v>
+        <v>-0.1808</v>
       </c>
       <c r="E21" t="n">
         <v>0.6603</v>
@@ -1422,7 +1422,7 @@
         <v>0.203</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1928</v>
+        <v>-0.2185</v>
       </c>
       <c r="E22" t="n">
         <v>0.5659</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5175</v>
+        <v>0.5161</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1857</v>
+        <v>0.1852</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2123</v>
+        <v>-0.2383</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5175</v>
+        <v>0.5161</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3665</v>
+        <v>0.3651</v>
       </c>
       <c r="G23" t="n">
         <v>0.151</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3665</v>
+        <v>0.3651</v>
       </c>
       <c r="I23" t="n">
         <v>0.3682</v>
@@ -1514,7 +1514,7 @@
         <v>0.1228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2831</v>
+        <v>-0.3076</v>
       </c>
       <c r="E24" t="n">
         <v>0.3422</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0045</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4265</v>
+        <v>-0.4489</v>
       </c>
       <c r="E25" t="n">
         <v>-0.0126</v>
@@ -1606,7 +1606,7 @@
         <v>-0.008800000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4312</v>
+        <v>-0.4536</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0244</v>
@@ -1652,7 +1652,7 @@
         <v>-0.09420000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5275</v>
+        <v>-0.5486</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2627</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1004</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5344</v>
+        <v>-0.5554</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2798</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4076</v>
+        <v>-0.4098</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1462</v>
+        <v>-0.147</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.586</v>
+        <v>-0.6072</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4076</v>
+        <v>-0.4098</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5924</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5924</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>0.5952</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.422</v>
+        <v>-0.4271</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1514</v>
+        <v>-0.1532</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5918</v>
+        <v>-0.6141</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.422</v>
+        <v>-0.4271</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3757</v>
+        <v>1.3706</v>
       </c>
       <c r="G30" t="n">
         <v>-1.7977</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3757</v>
+        <v>1.3706</v>
       </c>
       <c r="I30" t="n">
         <v>1.3821</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2007</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6473</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5594</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6985</v>
+        <v>-0.6993</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2506</v>
+        <v>-0.2509</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7035</v>
+        <v>-0.7225</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6985</v>
+        <v>-0.6993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2037</v>
+        <v>0.2029</v>
       </c>
       <c r="G32" t="n">
         <v>-0.9022</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2037</v>
+        <v>0.2029</v>
       </c>
       <c r="I32" t="n">
         <v>0.2046</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2924</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7506</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8149</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4065</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8791</v>
+        <v>-0.8953</v>
       </c>
       <c r="E34" t="n">
         <v>-1.133</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4589</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.9535</v>
       </c>
       <c r="E35" t="n">
         <v>-1.279</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5589</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0507</v>
+        <v>-1.0645</v>
       </c>
       <c r="E36" t="n">
         <v>-1.5578</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5666</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0594</v>
+        <v>-1.0731</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5793</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6032999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1007</v>
+        <v>-1.1139</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6816</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6248</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1249</v>
+        <v>-1.1377</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7415</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6395</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1415</v>
+        <v>-1.1541</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7826</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6646</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1697</v>
+        <v>-1.1819</v>
       </c>
       <c r="E41" t="n">
         <v>-1.8524</v>

--- a/database/event/6345/event_6345_evp_summary.xlsx
+++ b/database/event/6345/event_6345_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3971</v>
+        <v>8.5153</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0126</v>
+        <v>3.055</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9015</v>
+        <v>3.2062</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3971</v>
+        <v>8.5153</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8444</v>
+        <v>2.1784</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5527</v>
+        <v>6.3368</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8444</v>
+        <v>2.1784</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8599</v>
+        <v>2.268</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1751</v>
+        <v>6.3368</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>165</v>
       </c>
       <c r="M2" t="n">
-        <v>9.035</v>
+        <v>8.604800000000001</v>
       </c>
       <c r="N2" t="n">
         <v>295</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6249</v>
+        <v>6.3275</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3768</v>
+        <v>2.2701</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1955</v>
+        <v>2.2185</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6249</v>
+        <v>6.3275</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4922</v>
+        <v>3.1628</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1327</v>
+        <v>3.1647</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4922</v>
+        <v>3.5853</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5132</v>
+        <v>3.7327</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1327</v>
+        <v>3.1647</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>6.645899999999999</v>
+        <v>6.897399999999999</v>
       </c>
       <c r="N3" t="n">
         <v>331</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3875</v>
+        <v>5.5367</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2916</v>
+        <v>1.9864</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1009</v>
+        <v>1.8615</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3875</v>
+        <v>5.5367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4549</v>
+        <v>0.5306</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9326</v>
+        <v>5.0061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4549</v>
+        <v>0.5306</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4587</v>
+        <v>0.5524</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9326</v>
+        <v>5.0061</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>6.3913</v>
+        <v>5.5585</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1626</v>
+        <v>5.1912</v>
       </c>
       <c r="C5" t="n">
-        <v>2.211</v>
+        <v>1.8625</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0113</v>
+        <v>1.7056</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1626</v>
+        <v>5.1912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6768</v>
+        <v>0.824</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4858</v>
+        <v>4.3672</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6768</v>
+        <v>0.824</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6825</v>
+        <v>0.8579</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4858</v>
+        <v>4.3672</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>165</v>
       </c>
       <c r="M5" t="n">
-        <v>6.1683</v>
+        <v>5.2251</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9224</v>
+        <v>4.9055</v>
       </c>
       <c r="C6" t="n">
-        <v>1.766</v>
+        <v>1.7599</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5172</v>
+        <v>1.5766</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9224</v>
+        <v>4.9055</v>
       </c>
       <c r="F6" t="n">
-        <v>4.543</v>
+        <v>4.441</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3794</v>
+        <v>0.4645</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7169</v>
+        <v>10.1611</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6337</v>
+        <v>5.2833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3794</v>
+        <v>0.4645</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>5.013100000000001</v>
+        <v>5.7478</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4475</v>
+        <v>3.3048</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2369</v>
+        <v>1.1857</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9296</v>
+        <v>0.8539</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4475</v>
+        <v>3.3048</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0284</v>
+        <v>2.9683</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4191</v>
+        <v>0.3365</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0284</v>
+        <v>4.9722</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4546</v>
+        <v>2.5853</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4191</v>
+        <v>0.3365</v>
       </c>
       <c r="K7" t="n">
         <v>134</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8737</v>
+        <v>2.9218</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1641</v>
+        <v>3.1161</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1352</v>
+        <v>1.118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8167</v>
+        <v>0.7687</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1641</v>
+        <v>3.1161</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3573</v>
+        <v>3.1356</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1932</v>
+        <v>-0.0195</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3573</v>
+        <v>5.5616</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7212</v>
+        <v>2.8918</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1932</v>
+        <v>-0.0195</v>
       </c>
       <c r="K8" t="n">
         <v>148</v>
@@ -805,7 +805,7 @@
         <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.528</v>
+        <v>2.8723</v>
       </c>
       <c r="N8" t="n">
         <v>230</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5661</v>
+        <v>2.8863</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9206</v>
+        <v>1.0355</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5784</v>
+        <v>0.665</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5661</v>
+        <v>2.8863</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2631</v>
+        <v>2.6208</v>
       </c>
       <c r="G9" t="n">
-        <v>0.303</v>
+        <v>0.2655</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2631</v>
+        <v>3.7476</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8343</v>
+        <v>1.9486</v>
       </c>
       <c r="J9" t="n">
-        <v>0.303</v>
+        <v>0.2655</v>
       </c>
       <c r="K9" t="n">
         <v>148</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1373</v>
+        <v>2.2141</v>
       </c>
       <c r="N9" t="n">
         <v>230</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5421</v>
+        <v>2.759</v>
       </c>
       <c r="C10" t="n">
-        <v>0.912</v>
+        <v>0.9898</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5689</v>
+        <v>0.6075</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5421</v>
+        <v>2.759</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5558</v>
+        <v>1.806</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9863</v>
+        <v>0.953</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5558</v>
+        <v>1.806</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5689</v>
+        <v>1.8803</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9863</v>
+        <v>0.953</v>
       </c>
       <c r="K10" t="n">
         <v>130</v>
@@ -897,7 +897,7 @@
         <v>165</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5552</v>
+        <v>2.8333</v>
       </c>
       <c r="N10" t="n">
         <v>295</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3307</v>
+        <v>2.6949</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.9669</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4846</v>
+        <v>0.5786</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3307</v>
+        <v>2.6949</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2678</v>
+        <v>2.641</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0629</v>
+        <v>0.0539</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2678</v>
+        <v>3.8188</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8381</v>
+        <v>1.9856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0629</v>
+        <v>0.0539</v>
       </c>
       <c r="K11" t="n">
         <v>134</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>1.901</v>
+        <v>2.0395</v>
       </c>
       <c r="N11" t="n">
         <v>215</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9956</v>
+        <v>2.5565</v>
       </c>
       <c r="C12" t="n">
-        <v>0.716</v>
+        <v>0.9172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3511</v>
+        <v>0.5161</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9956</v>
+        <v>2.5565</v>
       </c>
       <c r="F12" t="n">
-        <v>2.298</v>
+        <v>2.6916</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3024</v>
+        <v>-0.1351</v>
       </c>
       <c r="H12" t="n">
-        <v>2.298</v>
+        <v>3.9973</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8626</v>
+        <v>2.0784</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3024</v>
+        <v>-0.1351</v>
       </c>
       <c r="K12" t="n">
         <v>134</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5602</v>
+        <v>1.9433</v>
       </c>
       <c r="N12" t="n">
         <v>215</v>
@@ -998,311 +998,311 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4863</v>
+        <v>1.9972</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5332</v>
+        <v>0.7165</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1482</v>
+        <v>0.2636</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4863</v>
+        <v>1.9972</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7083</v>
+        <v>2.0942</v>
       </c>
       <c r="G13" t="n">
-        <v>0.778</v>
+        <v>-0.097</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7083</v>
+        <v>2.0942</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7141999999999999</v>
+        <v>2.1803</v>
       </c>
       <c r="J13" t="n">
-        <v>0.778</v>
+        <v>-0.097</v>
       </c>
       <c r="K13" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="L13" t="n">
-        <v>189</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4922</v>
+        <v>2.0833</v>
       </c>
       <c r="N13" t="n">
-        <v>331</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0727</v>
+        <v>1.885</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3849</v>
+        <v>0.6763</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0165</v>
+        <v>0.213</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0727</v>
+        <v>1.885</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9876</v>
+        <v>1.9944</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0851</v>
+        <v>-0.1094</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9876</v>
+        <v>1.9944</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9959</v>
+        <v>1.037</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0851</v>
+        <v>-0.1094</v>
       </c>
       <c r="K14" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L14" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>1.081</v>
+        <v>0.9276</v>
       </c>
       <c r="N14" t="n">
-        <v>331</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9657</v>
+        <v>1.6504</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3465</v>
+        <v>0.5921</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0592</v>
+        <v>0.1071</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9657</v>
+        <v>1.6504</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0487</v>
+        <v>1.2818</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.083</v>
+        <v>0.3686</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0487</v>
+        <v>1.2818</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0575</v>
+        <v>1.3345</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.083</v>
+        <v>0.3686</v>
       </c>
       <c r="K15" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9745000000000001</v>
+        <v>1.7031</v>
       </c>
       <c r="N15" t="n">
-        <v>157</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9244</v>
+        <v>1.4585</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3316</v>
+        <v>0.5233</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0756</v>
+        <v>0.0204</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9244</v>
+        <v>1.4585</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1381</v>
+        <v>2.302</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2137</v>
+        <v>-0.8435</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1381</v>
+        <v>2.302</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9225</v>
+        <v>2.3967</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2137</v>
+        <v>-0.8435</v>
       </c>
       <c r="K16" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="L16" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7088</v>
+        <v>1.5532</v>
       </c>
       <c r="N16" t="n">
-        <v>215</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9052</v>
+        <v>1.4135</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3248</v>
+        <v>0.5071</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0833</v>
+        <v>0.0001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9052</v>
+        <v>1.4135</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7426</v>
+        <v>1.4541</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1626</v>
+        <v>-0.0406</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7426</v>
+        <v>1.4541</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7488</v>
+        <v>1.5139</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1626</v>
+        <v>-0.0406</v>
       </c>
       <c r="K17" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="L17" t="n">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9114</v>
+        <v>1.4733</v>
       </c>
       <c r="N17" t="n">
-        <v>295</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7749</v>
+        <v>1.2837</v>
       </c>
       <c r="C18" t="n">
-        <v>0.278</v>
+        <v>0.4606</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1352</v>
+        <v>-0.0585</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7749</v>
+        <v>1.2837</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0163</v>
+        <v>0.2515</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0322</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0746</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0163</v>
+        <v>0.2515</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7749</v>
+        <v>1.3261</v>
       </c>
       <c r="N18" t="n">
-        <v>180</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7307</v>
+        <v>1.0953</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2622</v>
+        <v>0.393</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1528</v>
+        <v>-0.1435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7307</v>
+        <v>1.0953</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7307</v>
+        <v>1.8715</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>-0.7762</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7307</v>
+        <v>1.8715</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7452</v>
+        <v>1.9485</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>-0.7762</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>39</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7452000000000001</v>
+        <v>1.1723</v>
       </c>
       <c r="N19" t="n">
         <v>157</v>
@@ -1320,415 +1320,415 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7167</v>
+        <v>1.0887</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2571</v>
+        <v>0.3906</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1584</v>
+        <v>-0.1465</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7167</v>
+        <v>1.0887</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7167</v>
+        <v>1.0887</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7167</v>
+        <v>1.0887</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7311</v>
+        <v>1.0887</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7311000000000001</v>
+        <v>1.0887</v>
       </c>
       <c r="N20" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6603</v>
+        <v>1.0409</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2369</v>
+        <v>0.3734</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1808</v>
+        <v>-0.1681</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6603</v>
+        <v>1.0409</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6603</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.2672</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6603</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6603</v>
+        <v>0.8055</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.2672</v>
       </c>
       <c r="K21" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6603</v>
+        <v>1.0727</v>
       </c>
       <c r="N21" t="n">
-        <v>114</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5659</v>
+        <v>0.9821</v>
       </c>
       <c r="C22" t="n">
-        <v>0.203</v>
+        <v>0.3523</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2185</v>
+        <v>-0.1946</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5659</v>
+        <v>0.9821</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5659</v>
+        <v>0.8294</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1527</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5659</v>
+        <v>0.8294</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5659</v>
+        <v>0.8294</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1527</v>
       </c>
       <c r="K22" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5659</v>
+        <v>0.9821</v>
       </c>
       <c r="N22" t="n">
-        <v>114</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5161</v>
+        <v>0.7844</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1852</v>
+        <v>0.2814</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2383</v>
+        <v>-0.2839</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5161</v>
+        <v>0.7844</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3651</v>
+        <v>0.8162</v>
       </c>
       <c r="G23" t="n">
-        <v>0.151</v>
+        <v>-0.0318</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3651</v>
+        <v>0.8162</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3682</v>
+        <v>0.4244</v>
       </c>
       <c r="J23" t="n">
-        <v>0.151</v>
+        <v>-0.0318</v>
       </c>
       <c r="K23" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5192</v>
+        <v>0.3926</v>
       </c>
       <c r="N23" t="n">
-        <v>331</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1228</v>
+        <v>0.2787</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3076</v>
+        <v>-0.2874</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3422</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0045</v>
+        <v>0.2071</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4489</v>
+        <v>-0.3774</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0126</v>
+        <v>0.5772</v>
       </c>
       <c r="N25" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>F1KU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0244</v>
+        <v>0.4466</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1602</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4536</v>
+        <v>-0.4364</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0244</v>
+        <v>0.4466</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6418</v>
+        <v>0.9101</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6662</v>
+        <v>-0.4635</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6418</v>
+        <v>0.9101</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6418</v>
+        <v>0.4732</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6662</v>
+        <v>-0.4635</v>
       </c>
       <c r="K26" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.02439999999999998</v>
+        <v>0.009699999999999986</v>
       </c>
       <c r="N26" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2627</v>
+        <v>0.4246</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.1523</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5486</v>
+        <v>-0.4463</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2627</v>
+        <v>0.4246</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1426</v>
+        <v>0.8486</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1201</v>
+        <v>-0.424</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1426</v>
+        <v>0.8486</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1156</v>
+        <v>0.8486</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1201</v>
+        <v>-0.424</v>
       </c>
       <c r="K27" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="L27" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2357</v>
+        <v>0.4246</v>
       </c>
       <c r="N27" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2798</v>
+        <v>0.3565</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1004</v>
+        <v>0.1279</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5554</v>
+        <v>-0.4771</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2798</v>
+        <v>0.3565</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0742</v>
+        <v>0.3565</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2056</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0742</v>
+        <v>0.3565</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0742</v>
+        <v>0.3565</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2056</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L28" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2798</v>
+        <v>0.3565</v>
       </c>
       <c r="N28" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4098</v>
+        <v>0.1481</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.147</v>
+        <v>0.0531</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6072</v>
+        <v>-0.5712</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4098</v>
+        <v>0.1481</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.8571</v>
       </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>-0.709</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.8571</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5952</v>
+        <v>0.8924</v>
       </c>
       <c r="J29" t="n">
-        <v>-1</v>
+        <v>-0.709</v>
       </c>
       <c r="K29" t="n">
         <v>118</v>
@@ -1771,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4048</v>
+        <v>0.1834</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4271</v>
+        <v>-0.0287</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1532</v>
+        <v>-0.0103</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6141</v>
+        <v>-0.651</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4271</v>
+        <v>-0.0287</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3706</v>
+        <v>0.6279</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.7977</v>
+        <v>-0.6566</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3706</v>
+        <v>0.6279</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3821</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.7977</v>
+        <v>-0.6566</v>
       </c>
       <c r="K30" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="L30" t="n">
-        <v>189</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4156</v>
+        <v>-0.002900000000000014</v>
       </c>
       <c r="N30" t="n">
-        <v>331</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F1KU</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5594</v>
+        <v>-0.0396</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2007</v>
+        <v>-0.0142</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6559</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5594</v>
+        <v>-0.0396</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1666</v>
+        <v>0.1149</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.726</v>
+        <v>-0.1545</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1666</v>
+        <v>0.1149</v>
       </c>
       <c r="I31" t="n">
-        <v>0.135</v>
+        <v>0.1149</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.726</v>
+        <v>-0.1545</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="L31" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.591</v>
+        <v>-0.0396</v>
       </c>
       <c r="N31" t="n">
-        <v>215</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6993</v>
+        <v>-0.4484</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2509</v>
+        <v>-0.1609</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7225</v>
+        <v>-0.8404</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6993</v>
+        <v>-0.4484</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2029</v>
+        <v>1.3998</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9022</v>
+        <v>-1.8482</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2029</v>
+        <v>1.3998</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2046</v>
+        <v>1.4574</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9022</v>
+        <v>-1.8482</v>
       </c>
       <c r="K32" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="L32" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6976</v>
+        <v>-0.3908</v>
       </c>
       <c r="N32" t="n">
-        <v>157</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8149</v>
+        <v>-0.5682</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2924</v>
+        <v>-0.2039</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.8945</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8149</v>
+        <v>-0.5682</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9166</v>
+        <v>-0.61</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1017</v>
+        <v>0.0418</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9166</v>
+        <v>-0.61</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9166</v>
+        <v>-0.61</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1017</v>
+        <v>0.0418</v>
       </c>
       <c r="K33" t="n">
         <v>118</v>
@@ -1955,7 +1955,7 @@
         <v>62</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8149</v>
+        <v>-0.5682</v>
       </c>
       <c r="N33" t="n">
         <v>180</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nython</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4065</v>
+        <v>-0.3019</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8953</v>
+        <v>-1.018</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.133</v>
+        <v>-0.8416</v>
       </c>
       <c r="N34" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>nython</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4589</v>
+        <v>-0.3168</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9535</v>
+        <v>-1.0366</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.279</v>
+        <v>-0.8829</v>
       </c>
       <c r="N35" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5578</v>
+        <v>-0.9658</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5589</v>
+        <v>-0.3465</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0645</v>
+        <v>-1.074</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5578</v>
+        <v>-0.9658</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.785</v>
+        <v>-0.4717</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7728</v>
+        <v>-0.4941</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.785</v>
+        <v>-0.4717</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.785</v>
+        <v>-0.4717</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7728</v>
+        <v>-0.4941</v>
       </c>
       <c r="K36" t="n">
         <v>118</v>
@@ -2093,7 +2093,7 @@
         <v>62</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5578</v>
+        <v>-0.9658</v>
       </c>
       <c r="N36" t="n">
         <v>180</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hardzao</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5666</v>
+        <v>-0.3924</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0731</v>
+        <v>-1.1318</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5793</v>
+        <v>-1.0938</v>
       </c>
       <c r="N37" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>hardzao</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.418</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1139</v>
+        <v>-1.164</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6816</v>
+        <v>-1.165</v>
       </c>
       <c r="N38" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6248</v>
+        <v>-0.5455</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1377</v>
+        <v>-1.3245</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7415</v>
+        <v>-1.5206</v>
       </c>
       <c r="N39" t="n">
         <v>112</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7826</v>
+        <v>-1.5706</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6395</v>
+        <v>-0.5635</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1541</v>
+        <v>-1.3471</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7826</v>
+        <v>-1.5706</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.1189</v>
+        <v>-1.5706</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3363</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.1189</v>
+        <v>-1.5706</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7174</v>
+        <v>-1.5706</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3363</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="L40" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3811</v>
+        <v>-1.5706</v>
       </c>
       <c r="N40" t="n">
-        <v>230</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8524</v>
+        <v>-1.8572</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6646</v>
+        <v>-0.6663</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1819</v>
+        <v>-1.4764</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8524</v>
+        <v>-1.8572</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8524</v>
+        <v>-2.1925</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.3353</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8524</v>
+        <v>-2.1925</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8524</v>
+        <v>-1.14</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.3353</v>
       </c>
       <c r="K41" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8524</v>
+        <v>-0.8047</v>
       </c>
       <c r="N41" t="n">
-        <v>112</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1929</v>
+        <v>1.1211</v>
       </c>
       <c r="J2" t="n">
-        <v>28.6296</v>
+        <v>26.9064</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9182</v>
+        <v>0.9143</v>
       </c>
       <c r="J3" t="n">
-        <v>22.0368</v>
+        <v>21.9432</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8507</v>
+        <v>0.8461</v>
       </c>
       <c r="J4" t="n">
-        <v>20.4168</v>
+        <v>20.3064</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4969</v>
+        <v>-0.4267</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.9256</v>
+        <v>-10.2408</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6018</v>
+        <v>-0.5377</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.4432</v>
+        <v>-12.9048</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4463</v>
+        <v>0.5129</v>
       </c>
       <c r="J7" t="n">
-        <v>10.7112</v>
+        <v>12.3096</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3912</v>
+        <v>-0.2544</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1163</v>
+        <v>-0.0915</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7912</v>
+        <v>-2.196</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3417</v>
+        <v>-0.2174</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.200799999999999</v>
+        <v>-5.2176</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6674</v>
+        <v>-0.4461</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.0176</v>
+        <v>-10.7064</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.89</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8138</v>
+        <v>1.5432</v>
       </c>
       <c r="J12" t="n">
-        <v>38.0898</v>
+        <v>32.4072</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3241</v>
+        <v>1.2346</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8061</v>
+        <v>25.9266</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.945</v>
+        <v>1.0348</v>
       </c>
       <c r="J14" t="n">
-        <v>19.845</v>
+        <v>21.7308</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.43</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9003</v>
+        <v>1.006</v>
       </c>
       <c r="J15" t="n">
-        <v>18.9063</v>
+        <v>21.126</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0332</v>
+        <v>0.0552</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6972</v>
+        <v>1.1592</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0779</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6359</v>
+        <v>-1.9383</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2529</v>
+        <v>-0.2182</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.3109</v>
+        <v>-4.5822</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.63</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4597</v>
+        <v>-0.3485</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.653700000000001</v>
+        <v>-7.3185</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7775</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.3275</v>
+        <v>-11.1888</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8804</v>
+        <v>-0.6093</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.4884</v>
+        <v>-12.7953</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5389</v>
+        <v>0.5141</v>
       </c>
       <c r="J22" t="n">
-        <v>15.6281</v>
+        <v>14.9089</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0328</v>
+        <v>0.0091</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9512</v>
+        <v>0.2639</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.15</v>
+        <v>-0.0948</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.35</v>
+        <v>-2.7492</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.15</v>
+        <v>-0.0948</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.35</v>
+        <v>-2.7492</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6742</v>
+        <v>-0.4509</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.5518</v>
+        <v>-13.0761</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1959</v>
+        <v>0.849</v>
       </c>
       <c r="J27" t="n">
-        <v>34.6811</v>
+        <v>24.621</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0301</v>
+        <v>0.7441</v>
       </c>
       <c r="J28" t="n">
-        <v>29.8729</v>
+        <v>21.5789</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3682</v>
+        <v>0.3829</v>
       </c>
       <c r="J29" t="n">
-        <v>10.6778</v>
+        <v>11.1041</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3811</v>
+        <v>-0.3068</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.0519</v>
+        <v>-8.8972</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4395</v>
+        <v>-0.3671</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.7455</v>
+        <v>-10.6459</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.707</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>16.968</v>
+        <v>12.1584</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5131</v>
+        <v>0.401</v>
       </c>
       <c r="J33" t="n">
-        <v>12.3144</v>
+        <v>9.624000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.391</v>
+        <v>0.3372</v>
       </c>
       <c r="J34" t="n">
-        <v>9.384</v>
+        <v>8.0928</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2383</v>
+        <v>-0.131</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.7192</v>
+        <v>-3.144</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2548</v>
+        <v>-0.1425</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.1152</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3502</v>
+        <v>0.2943</v>
       </c>
       <c r="J37" t="n">
-        <v>8.4048</v>
+        <v>7.0632</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2141</v>
+        <v>-0.1442</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.1384</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2338</v>
+        <v>-0.1545</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.6112</v>
+        <v>-3.708</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.27</v>
+        <v>-0.175</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.48</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5099</v>
+        <v>-0.3321</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.2376</v>
+        <v>-7.9704</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1951</v>
+        <v>0.2063</v>
       </c>
       <c r="J42" t="n">
-        <v>5.6579</v>
+        <v>5.9827</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0953</v>
+        <v>0.0929</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7637</v>
+        <v>2.6941</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0953</v>
+        <v>0.0929</v>
       </c>
       <c r="J44" t="n">
-        <v>2.7637</v>
+        <v>2.6941</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1529</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.4341</v>
+        <v>-2.5375</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2429</v>
+        <v>-0.1446</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.0441</v>
+        <v>-4.1934</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9734</v>
+        <v>0.7003</v>
       </c>
       <c r="J47" t="n">
-        <v>28.2286</v>
+        <v>20.3087</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4022</v>
+        <v>0.3623</v>
       </c>
       <c r="J48" t="n">
-        <v>11.6638</v>
+        <v>10.5067</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3401</v>
+        <v>0.3249</v>
       </c>
       <c r="J49" t="n">
-        <v>9.8629</v>
+        <v>9.4221</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0665</v>
+        <v>-0.0167</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.9285</v>
+        <v>-0.4843</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6705</v>
+        <v>-0.6171</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.4445</v>
+        <v>-17.8959</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0621</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.5525</v>
+        <v>-1.5925</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.91</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1402</v>
+        <v>-0.1113</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.505</v>
+        <v>-2.7825</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1791</v>
+        <v>-0.1331</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.4775</v>
+        <v>-3.3275</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3151</v>
+        <v>-0.204</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.8775</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3313</v>
+        <v>-0.2139</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.282500000000001</v>
+        <v>-5.3475</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1626</v>
+        <v>0.8296</v>
       </c>
       <c r="J57" t="n">
-        <v>29.065</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8851</v>
+        <v>0.6589</v>
       </c>
       <c r="J58" t="n">
-        <v>22.1275</v>
+        <v>16.4725</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.25</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6711</v>
+        <v>0.5366</v>
       </c>
       <c r="J59" t="n">
-        <v>16.7775</v>
+        <v>13.415</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0509</v>
+        <v>0.1197</v>
       </c>
       <c r="J60" t="n">
-        <v>1.2725</v>
+        <v>2.9925</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5029</v>
+        <v>-0.4317</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.5725</v>
+        <v>-10.7925</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4968</v>
+        <v>0.388</v>
       </c>
       <c r="J62" t="n">
-        <v>14.904</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.266</v>
+        <v>0.2276</v>
       </c>
       <c r="J63" t="n">
-        <v>7.98</v>
+        <v>6.828</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1689</v>
+        <v>0.1617</v>
       </c>
       <c r="J64" t="n">
-        <v>5.067</v>
+        <v>4.851</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.112</v>
+        <v>0.1185</v>
       </c>
       <c r="J65" t="n">
-        <v>3.36</v>
+        <v>3.555</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2063</v>
+        <v>-0.1119</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.189</v>
+        <v>-3.357</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6606</v>
+        <v>0.5016</v>
       </c>
       <c r="J67" t="n">
-        <v>19.818</v>
+        <v>15.048</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2805</v>
+        <v>0.236</v>
       </c>
       <c r="J68" t="n">
-        <v>8.414999999999999</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0882</v>
+        <v>-0.0493</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.646</v>
+        <v>-1.479</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3961</v>
+        <v>-0.2481</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.883</v>
+        <v>-7.443</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5702</v>
+        <v>-0.373</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.106</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1014</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>2.6364</v>
+        <v>2.1216</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0056</v>
+        <v>-0.014</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1456</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1414</v>
+        <v>-1.1466</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2533</v>
+        <v>-0.1587</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.5858</v>
+        <v>-4.1262</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3795</v>
+        <v>-0.2403</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.867000000000001</v>
+        <v>-6.2478</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.98</v>
       </c>
       <c r="I77" t="n">
-        <v>1.9191</v>
+        <v>1.4491</v>
       </c>
       <c r="J77" t="n">
-        <v>49.8966</v>
+        <v>37.6766</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>1.2513</v>
+        <v>0.8879</v>
       </c>
       <c r="J78" t="n">
-        <v>32.5338</v>
+        <v>23.0854</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.38</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9608</v>
+        <v>0.7075</v>
       </c>
       <c r="J79" t="n">
-        <v>24.9808</v>
+        <v>18.395</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.9381</v>
+        <v>-0.9051</v>
       </c>
       <c r="J80" t="n">
-        <v>-24.3906</v>
+        <v>-23.5326</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.52</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3252</v>
+        <v>-1.3485</v>
       </c>
       <c r="J81" t="n">
-        <v>-34.4552</v>
+        <v>-35.061</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.44</v>
       </c>
       <c r="I82" t="n">
-        <v>1.111</v>
+        <v>0.7954</v>
       </c>
       <c r="J82" t="n">
-        <v>28.886</v>
+        <v>20.6804</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>0.984</v>
+        <v>0.7163</v>
       </c>
       <c r="J83" t="n">
-        <v>25.584</v>
+        <v>18.6238</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.31</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8278</v>
+        <v>0.6221</v>
       </c>
       <c r="J84" t="n">
-        <v>21.5228</v>
+        <v>16.1746</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4695</v>
+        <v>-0.3979</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.207</v>
+        <v>-10.3454</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5762</v>
+        <v>-0.5105</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.9812</v>
+        <v>-13.273</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0689</v>
+        <v>0.0327</v>
       </c>
       <c r="J87" t="n">
-        <v>1.7914</v>
+        <v>0.8502</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0353</v>
+        <v>-0.0484</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-1.2584</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3574</v>
+        <v>-0.232</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.292400000000001</v>
+        <v>-6.032</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3574</v>
+        <v>-0.232</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.292400000000001</v>
+        <v>-6.032</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3882</v>
+        <v>-0.2516</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.0932</v>
+        <v>-6.5416</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2432</v>
+        <v>0.8786</v>
       </c>
       <c r="J92" t="n">
-        <v>44.7552</v>
+        <v>31.6296</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.48</v>
       </c>
       <c r="I93" t="n">
-        <v>1.203</v>
+        <v>0.8526</v>
       </c>
       <c r="J93" t="n">
-        <v>43.308</v>
+        <v>30.6936</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.24</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6718</v>
+        <v>0.5286</v>
       </c>
       <c r="J94" t="n">
-        <v>24.1848</v>
+        <v>19.0296</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4631</v>
+        <v>-0.3928</v>
       </c>
       <c r="J95" t="n">
-        <v>-16.6716</v>
+        <v>-14.1408</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.0112</v>
+        <v>-0.9875</v>
       </c>
       <c r="J96" t="n">
-        <v>-36.4032</v>
+        <v>-35.55</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3737</v>
+        <v>0.3847</v>
       </c>
       <c r="J97" t="n">
-        <v>13.4532</v>
+        <v>13.8492</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0328</v>
+        <v>0.0091</v>
       </c>
       <c r="J98" t="n">
-        <v>1.1808</v>
+        <v>0.3276</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1703</v>
+        <v>-0.1061</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.1308</v>
+        <v>-3.8196</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3088</v>
+        <v>-0.192</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.1168</v>
+        <v>-6.912</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3846</v>
+        <v>-0.2425</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.8456</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.01</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1209</v>
+        <v>0.0883</v>
       </c>
       <c r="J102" t="n">
-        <v>2.6598</v>
+        <v>1.9426</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2568</v>
+        <v>-0.1887</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.6496</v>
+        <v>-4.1514</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3548</v>
+        <v>-0.2366</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.8056</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3711</v>
+        <v>-0.2462</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.164199999999999</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4622</v>
+        <v>-0.3038</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.1684</v>
+        <v>-6.6836</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.579</v>
+        <v>1.107</v>
       </c>
       <c r="J107" t="n">
-        <v>34.738</v>
+        <v>24.354</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.56</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2779</v>
+        <v>0.9143</v>
       </c>
       <c r="J108" t="n">
-        <v>28.1138</v>
+        <v>20.1146</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.44</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0327</v>
+        <v>0.7661</v>
       </c>
       <c r="J109" t="n">
-        <v>22.7194</v>
+        <v>16.8542</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0372</v>
+        <v>0.1209</v>
       </c>
       <c r="J110" t="n">
-        <v>0.8184</v>
+        <v>2.6598</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5369</v>
+        <v>-0.4628</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.8118</v>
+        <v>-10.1816</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.75</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2039</v>
+        <v>-0.1853</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.4663</v>
+        <v>-3.1501</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.53</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5474</v>
+        <v>-0.42</v>
       </c>
       <c r="J113" t="n">
-        <v>-9.3058</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.75</v>
+        <v>-0.5203</v>
       </c>
       <c r="J114" t="n">
-        <v>-12.75</v>
+        <v>-8.8451</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.41</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7649</v>
+        <v>-0.53</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.0033</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7796</v>
+        <v>-0.5397</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.2532</v>
+        <v>-9.174899999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.29</v>
       </c>
       <c r="I117" t="n">
-        <v>2.0877</v>
+        <v>1.6615</v>
       </c>
       <c r="J117" t="n">
-        <v>35.4909</v>
+        <v>28.2455</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>1.123</v>
+        <v>0.8974</v>
       </c>
       <c r="J118" t="n">
-        <v>19.091</v>
+        <v>15.2558</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.55</v>
       </c>
       <c r="I119" t="n">
-        <v>1.0641</v>
+        <v>0.8626</v>
       </c>
       <c r="J119" t="n">
-        <v>18.0897</v>
+        <v>14.6642</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.55</v>
       </c>
       <c r="I120" t="n">
-        <v>1.0641</v>
+        <v>0.8626</v>
       </c>
       <c r="J120" t="n">
-        <v>18.0897</v>
+        <v>14.6642</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.45</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8676</v>
+        <v>0.7427</v>
       </c>
       <c r="J121" t="n">
-        <v>14.7492</v>
+        <v>12.6259</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2964</v>
+        <v>1.1846</v>
       </c>
       <c r="J122" t="n">
-        <v>37.5956</v>
+        <v>34.3534</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5845</v>
+        <v>0.5598</v>
       </c>
       <c r="J123" t="n">
-        <v>16.9505</v>
+        <v>16.2342</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2086</v>
+        <v>0.2395</v>
       </c>
       <c r="J124" t="n">
-        <v>6.0494</v>
+        <v>6.9455</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3818</v>
+        <v>-0.3165</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.0722</v>
+        <v>-9.1785</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7488</v>
+        <v>-0.6997</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.7152</v>
+        <v>-20.2913</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4468</v>
+        <v>0.5184</v>
       </c>
       <c r="J127" t="n">
-        <v>12.9572</v>
+        <v>15.0336</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3761</v>
+        <v>0.4268</v>
       </c>
       <c r="J128" t="n">
-        <v>10.9069</v>
+        <v>12.3772</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1666</v>
+        <v>-0.098</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.8314</v>
+        <v>-2.842</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.85</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.801500000000001</v>
+        <v>-5.3824</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5296</v>
+        <v>-0.3434</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.3584</v>
+        <v>-9.958600000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.054</v>
+        <v>1.0519</v>
       </c>
       <c r="J132" t="n">
-        <v>26.35</v>
+        <v>26.2975</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="J133" t="n">
-        <v>24.18</v>
+        <v>24.8225</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.637</v>
+        <v>0.7237</v>
       </c>
       <c r="J134" t="n">
-        <v>15.925</v>
+        <v>18.0925</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6126</v>
+        <v>0.7009</v>
       </c>
       <c r="J135" t="n">
-        <v>15.315</v>
+        <v>17.5225</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.25</v>
       </c>
       <c r="I136" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>14.1</v>
+        <v>16.3675</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2635</v>
+        <v>0.2674</v>
       </c>
       <c r="J137" t="n">
-        <v>6.5875</v>
+        <v>6.685</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2275</v>
+        <v>0.2212</v>
       </c>
       <c r="J138" t="n">
-        <v>5.6875</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.71</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4622</v>
+        <v>-0.3038</v>
       </c>
       <c r="J139" t="n">
-        <v>-11.555</v>
+        <v>-7.595</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.67</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5188</v>
+        <v>-0.3418</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.97</v>
+        <v>-8.545</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6384</v>
+        <v>-0.4262</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.96</v>
+        <v>-10.655</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.74</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6654</v>
+        <v>1.4348</v>
       </c>
       <c r="J142" t="n">
-        <v>43.3004</v>
+        <v>37.3048</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7054</v>
+        <v>0.719</v>
       </c>
       <c r="J143" t="n">
-        <v>18.3404</v>
+        <v>18.694</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3377</v>
+        <v>0.4063</v>
       </c>
       <c r="J144" t="n">
-        <v>8.780200000000001</v>
+        <v>10.5638</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0064</v>
+        <v>0.079</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1664</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.397</v>
+        <v>-0.3194</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.322</v>
+        <v>-8.304399999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3411</v>
+        <v>0.3698</v>
       </c>
       <c r="J147" t="n">
-        <v>8.868600000000001</v>
+        <v>9.614800000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2037</v>
+        <v>0.1918</v>
       </c>
       <c r="J148" t="n">
-        <v>5.2962</v>
+        <v>4.9868</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3765</v>
+        <v>-0.2478</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.789</v>
+        <v>-6.4428</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5085</v>
+        <v>-0.334</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.221</v>
+        <v>-8.683999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7037</v>
+        <v>-0.474</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.2962</v>
+        <v>-12.324</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.88</v>
+        <v>0.8731</v>
       </c>
       <c r="J152" t="n">
-        <v>21.12</v>
+        <v>20.9544</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.21</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5891</v>
+        <v>0.59</v>
       </c>
       <c r="J153" t="n">
-        <v>14.1384</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4029</v>
+        <v>0.4436</v>
       </c>
       <c r="J154" t="n">
-        <v>9.669600000000001</v>
+        <v>10.6464</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2544</v>
+        <v>0.3103</v>
       </c>
       <c r="J155" t="n">
-        <v>6.1056</v>
+        <v>7.4472</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.04</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0648</v>
+        <v>0.1277</v>
       </c>
       <c r="J156" t="n">
-        <v>1.5552</v>
+        <v>3.0648</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0665</v>
+        <v>-0.0709</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.596</v>
+        <v>-1.7016</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1413</v>
+        <v>-0.1181</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.3912</v>
+        <v>-2.8344</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1777</v>
+        <v>-0.14</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.2648</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2589</v>
+        <v>-0.1807</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.2136</v>
+        <v>-4.3368</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5521</v>
+        <v>-0.3638</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.2504</v>
+        <v>-8.731199999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6645</v>
+        <v>0.5956</v>
       </c>
       <c r="J162" t="n">
-        <v>15.2835</v>
+        <v>13.6988</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4626</v>
+        <v>0.4219</v>
       </c>
       <c r="J163" t="n">
-        <v>10.6398</v>
+        <v>9.7037</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.29</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3976</v>
+        <v>0.3782</v>
       </c>
       <c r="J164" t="n">
-        <v>9.1448</v>
+        <v>8.698600000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2493</v>
+        <v>0.2606</v>
       </c>
       <c r="J165" t="n">
-        <v>5.7339</v>
+        <v>5.9938</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.22</v>
+        <v>0.2353</v>
       </c>
       <c r="J166" t="n">
-        <v>5.06</v>
+        <v>5.4119</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.21</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4537</v>
+        <v>0.3991</v>
       </c>
       <c r="J167" t="n">
-        <v>10.4351</v>
+        <v>9.1793</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1566</v>
+        <v>0.1031</v>
       </c>
       <c r="J168" t="n">
-        <v>3.6018</v>
+        <v>2.3713</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.428</v>
+        <v>-0.2789</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.843999999999999</v>
+        <v>-6.4147</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.3423</v>
+        <v>-8.818199999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.3423</v>
+        <v>-8.818199999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4611</v>
+        <v>0.5406</v>
       </c>
       <c r="J172" t="n">
-        <v>13.3719</v>
+        <v>15.6774</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3331</v>
+        <v>0.3777</v>
       </c>
       <c r="J173" t="n">
-        <v>9.6599</v>
+        <v>10.9533</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.12</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2545</v>
+        <v>0.282</v>
       </c>
       <c r="J174" t="n">
-        <v>7.3805</v>
+        <v>8.178000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2982</v>
+        <v>-0.1795</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.6478</v>
+        <v>-5.2055</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5492</v>
+        <v>-0.3571</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.9268</v>
+        <v>-10.3559</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8777</v>
+        <v>0.8558</v>
       </c>
       <c r="J177" t="n">
-        <v>25.4533</v>
+        <v>24.8182</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6893</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>19.9897</v>
+        <v>19.1922</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.292</v>
+        <v>0.2973</v>
       </c>
       <c r="J179" t="n">
-        <v>8.468</v>
+        <v>8.621700000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2151</v>
+        <v>-0.1527</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.2379</v>
+        <v>-4.4283</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5991</v>
+        <v>-0.5409</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.3739</v>
+        <v>-15.6861</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.3751</v>
+        <v>-0.2959</v>
       </c>
       <c r="J182" t="n">
-        <v>-7.8771</v>
+        <v>-6.2139</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.67</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4076</v>
+        <v>-0.3152</v>
       </c>
       <c r="J183" t="n">
-        <v>-8.5596</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.62</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.5062</v>
+        <v>-0.3599</v>
       </c>
       <c r="J184" t="n">
-        <v>-10.6302</v>
+        <v>-7.5579</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.59</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5579</v>
+        <v>-0.3868</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.7159</v>
+        <v>-8.1228</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5737</v>
+        <v>-0.396</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.0477</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.02</v>
       </c>
       <c r="I187" t="n">
-        <v>1.9848</v>
+        <v>1.6885</v>
       </c>
       <c r="J187" t="n">
-        <v>41.6808</v>
+        <v>35.4585</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>2.02</v>
       </c>
       <c r="I188" t="n">
-        <v>1.9848</v>
+        <v>1.6885</v>
       </c>
       <c r="J188" t="n">
-        <v>41.6808</v>
+        <v>35.4585</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.3</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6166</v>
+        <v>0.7389</v>
       </c>
       <c r="J189" t="n">
-        <v>12.9486</v>
+        <v>15.5169</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3427</v>
+        <v>0.452</v>
       </c>
       <c r="J190" t="n">
-        <v>7.1967</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.91</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5135</v>
+        <v>-0.4357</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.7835</v>
+        <v>-9.149699999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3784</v>
+        <v>0.4479</v>
       </c>
       <c r="J192" t="n">
-        <v>7.1896</v>
+        <v>8.5101</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.4953</v>
+        <v>-0.3721</v>
       </c>
       <c r="J193" t="n">
-        <v>-9.4107</v>
+        <v>-7.0699</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.5</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.6722</v>
+        <v>-0.4622</v>
       </c>
       <c r="J194" t="n">
-        <v>-12.7718</v>
+        <v>-8.7818</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7431</v>
+        <v>-0.5095</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.1189</v>
+        <v>-9.6805</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9381</v>
+        <v>-0.6539</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.8239</v>
+        <v>-12.4241</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.81</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6725</v>
+        <v>1.4518</v>
       </c>
       <c r="J197" t="n">
-        <v>31.7775</v>
+        <v>27.5842</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.7</v>
       </c>
       <c r="I198" t="n">
-        <v>1.4736</v>
+        <v>1.3262</v>
       </c>
       <c r="J198" t="n">
-        <v>27.9984</v>
+        <v>25.1978</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.67</v>
       </c>
       <c r="I199" t="n">
-        <v>1.4174</v>
+        <v>1.2917</v>
       </c>
       <c r="J199" t="n">
-        <v>26.9306</v>
+        <v>24.5423</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.22</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4349</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>8.2631</v>
+        <v>10.4481</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0275</v>
+        <v>0.1189</v>
       </c>
       <c r="J201" t="n">
-        <v>0.5225</v>
+        <v>2.2591</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.72</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9645</v>
+        <v>0.8818</v>
       </c>
       <c r="J202" t="n">
-        <v>27.006</v>
+        <v>24.6904</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0285</v>
+        <v>0.0521</v>
       </c>
       <c r="J203" t="n">
-        <v>0.798</v>
+        <v>1.4588</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.02</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0062</v>
+        <v>0.0335</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1736</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1728</v>
+        <v>-0.0888</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.8384</v>
+        <v>-2.4864</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2594</v>
+        <v>-0.1477</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.2632</v>
+        <v>-4.1356</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4413</v>
+        <v>0.3923</v>
       </c>
       <c r="J207" t="n">
-        <v>12.3564</v>
+        <v>10.9844</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4135</v>
+        <v>0.3647</v>
       </c>
       <c r="J208" t="n">
-        <v>11.578</v>
+        <v>10.2116</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I209" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="J209" t="n">
-        <v>2.6404</v>
+        <v>1.9824</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4528</v>
+        <v>-0.2878</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.6784</v>
+        <v>-8.058400000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4664</v>
+        <v>-0.2975</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.0592</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.84</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.127</v>
+        <v>-0.1283</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.54</v>
+        <v>-2.566</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.74</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2839</v>
+        <v>-0.2395</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.678</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5927</v>
+        <v>-0.4106</v>
       </c>
       <c r="J214" t="n">
-        <v>-11.854</v>
+        <v>-8.212</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6082</v>
+        <v>-0.4198</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.164</v>
+        <v>-8.396000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.35</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8804</v>
+        <v>-0.6093</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.608</v>
+        <v>-12.186</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6046</v>
+        <v>1.4013</v>
       </c>
       <c r="J217" t="n">
-        <v>32.092</v>
+        <v>28.026</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1665</v>
+        <v>1.1285</v>
       </c>
       <c r="J218" t="n">
-        <v>23.33</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.5</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1252</v>
+        <v>1.1044</v>
       </c>
       <c r="J219" t="n">
-        <v>22.504</v>
+        <v>22.088</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4172</v>
+        <v>0.5205</v>
       </c>
       <c r="J220" t="n">
-        <v>8.343999999999999</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.02</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.0014</v>
       </c>
       <c r="J221" t="n">
-        <v>-1.662</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4967</v>
+        <v>0.4656</v>
       </c>
       <c r="J222" t="n">
-        <v>17.3845</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4967</v>
+        <v>0.4656</v>
       </c>
       <c r="J223" t="n">
-        <v>17.3845</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0463</v>
+        <v>0.0814</v>
       </c>
       <c r="J224" t="n">
-        <v>1.6205</v>
+        <v>2.849</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0463</v>
+        <v>0.0814</v>
       </c>
       <c r="J225" t="n">
-        <v>1.6205</v>
+        <v>2.849</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1636</v>
+        <v>-0.1092</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.726</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5322</v>
+        <v>0.6362</v>
       </c>
       <c r="J227" t="n">
-        <v>18.627</v>
+        <v>22.267</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5322</v>
+        <v>0.6362</v>
       </c>
       <c r="J228" t="n">
-        <v>18.627</v>
+        <v>22.267</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.96</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1304</v>
+        <v>-0.0674</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.564</v>
+        <v>-2.359</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.83</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3494</v>
+        <v>-0.2134</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.229</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4208</v>
+        <v>-0.2637</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.728</v>
+        <v>-9.2295</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3367</v>
+        <v>0.2908</v>
       </c>
       <c r="J232" t="n">
-        <v>9.7643</v>
+        <v>8.433199999999999</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2009</v>
+        <v>0.1649</v>
       </c>
       <c r="J233" t="n">
-        <v>5.8261</v>
+        <v>4.7821</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0727</v>
+        <v>0.0538</v>
       </c>
       <c r="J234" t="n">
-        <v>2.1083</v>
+        <v>1.5602</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2688</v>
+        <v>-0.2285</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.7952</v>
+        <v>-6.6265</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.92</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3341</v>
+        <v>-0.2896</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.6889</v>
+        <v>-8.398400000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6823</v>
+        <v>0.8403</v>
       </c>
       <c r="J237" t="n">
-        <v>19.7867</v>
+        <v>24.3687</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.3</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4965</v>
+        <v>0.5924</v>
       </c>
       <c r="J238" t="n">
-        <v>14.3985</v>
+        <v>17.1796</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.95</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1594</v>
+        <v>-0.0833</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.6226</v>
+        <v>-2.4157</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1964</v>
+        <v>-0.1077</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.6956</v>
+        <v>-3.1233</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4934</v>
+        <v>-0.3154</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.3086</v>
+        <v>-9.146599999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6508</v>
       </c>
       <c r="J242" t="n">
-        <v>16.6819</v>
+        <v>14.9684</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6443</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>14.8189</v>
+        <v>13.2503</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1932</v>
+        <v>0.2107</v>
       </c>
       <c r="J244" t="n">
-        <v>4.4436</v>
+        <v>4.8461</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1932</v>
+        <v>0.2107</v>
       </c>
       <c r="J245" t="n">
-        <v>4.4436</v>
+        <v>4.8461</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.1</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1157</v>
+        <v>0.1424</v>
       </c>
       <c r="J246" t="n">
-        <v>2.6611</v>
+        <v>3.2752</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.228</v>
+        <v>0.1725</v>
       </c>
       <c r="J247" t="n">
-        <v>5.244</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.06</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2097</v>
+        <v>0.1549</v>
       </c>
       <c r="J248" t="n">
-        <v>4.8231</v>
+        <v>3.5627</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3262</v>
+        <v>-0.2125</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.5026</v>
+        <v>-4.8875</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3889</v>
+        <v>-0.2519</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.944699999999999</v>
+        <v>-5.7937</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6096</v>
+        <v>-0.4042</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.0208</v>
+        <v>-9.2966</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.17</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3509</v>
+        <v>0.3931</v>
       </c>
       <c r="J252" t="n">
-        <v>9.825200000000001</v>
+        <v>11.0068</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3206</v>
+        <v>0.3547</v>
       </c>
       <c r="J253" t="n">
-        <v>8.976800000000001</v>
+        <v>9.9316</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0973</v>
+        <v>-0.0605</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.7244</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1202</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.3656</v>
+        <v>-2.0412</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6288</v>
+        <v>-0.4166</v>
       </c>
       <c r="J256" t="n">
-        <v>-17.6064</v>
+        <v>-11.6648</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7803</v>
+        <v>0.7483</v>
       </c>
       <c r="J257" t="n">
-        <v>21.8484</v>
+        <v>20.9524</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J258" t="n">
-        <v>17.7408</v>
+        <v>16.7468</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.15</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5019</v>
+        <v>0.4681</v>
       </c>
       <c r="J259" t="n">
-        <v>14.0532</v>
+        <v>13.1068</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.159</v>
+        <v>-0.1071</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.452</v>
+        <v>-2.9988</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.9439</v>
+        <v>-0.914</v>
       </c>
       <c r="J261" t="n">
-        <v>-26.4292</v>
+        <v>-25.592</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.22</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4303</v>
+        <v>0.4941</v>
       </c>
       <c r="J262" t="n">
-        <v>12.4787</v>
+        <v>14.3289</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.01</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0672</v>
+        <v>0.0474</v>
       </c>
       <c r="J263" t="n">
-        <v>1.9488</v>
+        <v>1.3746</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0038</v>
+        <v>-0.0164</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.1102</v>
+        <v>-0.4756</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4281</v>
+        <v>-0.2724</v>
       </c>
       <c r="J265" t="n">
-        <v>-12.4149</v>
+        <v>-7.8996</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4281</v>
+        <v>-0.2724</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.4149</v>
+        <v>-7.8996</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.42</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0529</v>
+        <v>1.034</v>
       </c>
       <c r="J267" t="n">
-        <v>30.5341</v>
+        <v>29.986</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.24</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6365</v>
+        <v>0.652</v>
       </c>
       <c r="J268" t="n">
-        <v>18.4585</v>
+        <v>18.908</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5127</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J269" t="n">
-        <v>14.8683</v>
+        <v>16.211</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.26</v>
+        <v>0.3281</v>
       </c>
       <c r="J270" t="n">
-        <v>7.54</v>
+        <v>9.514900000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.08</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1727</v>
+        <v>0.2424</v>
       </c>
       <c r="J271" t="n">
-        <v>5.0083</v>
+        <v>7.0296</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.38</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6576</v>
+        <v>0.6162</v>
       </c>
       <c r="J272" t="n">
-        <v>17.0976</v>
+        <v>16.0212</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4345</v>
+        <v>0.3801</v>
       </c>
       <c r="J273" t="n">
-        <v>11.297</v>
+        <v>9.8826</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.74</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4433</v>
+        <v>-0.2855</v>
       </c>
       <c r="J274" t="n">
-        <v>-11.5258</v>
+        <v>-7.423</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.71</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4851</v>
+        <v>-0.3144</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.6126</v>
+        <v>-8.1744</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.45</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8092</v>
+        <v>-0.5543</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.0392</v>
+        <v>-14.4118</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.64</v>
       </c>
       <c r="I277" t="n">
-        <v>0.871</v>
+        <v>0.7867</v>
       </c>
       <c r="J277" t="n">
-        <v>22.646</v>
+        <v>20.4542</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6337</v>
+        <v>0.5556</v>
       </c>
       <c r="J278" t="n">
-        <v>16.4762</v>
+        <v>14.4456</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0604</v>
+        <v>-0.0142</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.5704</v>
+        <v>-0.3692</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3121</v>
+        <v>-0.1835</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.114599999999999</v>
+        <v>-4.771</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3708</v>
+        <v>-0.2252</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.6408</v>
+        <v>-5.8552</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.482</v>
+        <v>1.3098</v>
       </c>
       <c r="J282" t="n">
-        <v>35.568</v>
+        <v>31.4352</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8456</v>
+        <v>0.8336</v>
       </c>
       <c r="J283" t="n">
-        <v>20.2944</v>
+        <v>20.0064</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.25</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7039</v>
+        <v>0.6916</v>
       </c>
       <c r="J284" t="n">
-        <v>16.8936</v>
+        <v>16.5984</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5924</v>
+        <v>-0.5295</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.2176</v>
+        <v>-12.708</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.7</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.944</v>
+        <v>-0.9122</v>
       </c>
       <c r="J286" t="n">
-        <v>-22.656</v>
+        <v>-21.8928</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.8275</v>
       </c>
       <c r="J287" t="n">
-        <v>16.1496</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.89</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1922</v>
+        <v>-0.1341</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.6128</v>
+        <v>-3.2184</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3367</v>
+        <v>-0.2157</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.0808</v>
+        <v>-5.1768</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.4552</v>
+        <v>-5.4144</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6773</v>
+        <v>-0.4536</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.2552</v>
+        <v>-10.8864</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.59</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3399</v>
+        <v>1.2261</v>
       </c>
       <c r="J292" t="n">
-        <v>33.4975</v>
+        <v>30.6525</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1415</v>
+        <v>1.1033</v>
       </c>
       <c r="J293" t="n">
-        <v>28.5375</v>
+        <v>27.5825</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.927</v>
+        <v>0.9587</v>
       </c>
       <c r="J294" t="n">
-        <v>23.175</v>
+        <v>23.9675</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.35</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8326</v>
+        <v>0.877</v>
       </c>
       <c r="J295" t="n">
-        <v>20.815</v>
+        <v>21.925</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7024</v>
       </c>
       <c r="J296" t="n">
-        <v>-18.915</v>
+        <v>-17.56</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2307</v>
+        <v>0.2231</v>
       </c>
       <c r="J297" t="n">
-        <v>5.7675</v>
+        <v>5.5775</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3332</v>
+        <v>-0.2408</v>
       </c>
       <c r="J298" t="n">
-        <v>-8.33</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.74</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3934</v>
+        <v>-0.2683</v>
       </c>
       <c r="J299" t="n">
-        <v>-9.835000000000001</v>
+        <v>-6.7075</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.64</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5442</v>
+        <v>-0.3625</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.605</v>
+        <v>-9.0625</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5442</v>
+        <v>-0.3625</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.605</v>
+        <v>-9.0625</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.7</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5479</v>
+        <v>1.3597</v>
       </c>
       <c r="J302" t="n">
-        <v>35.6017</v>
+        <v>31.2731</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1841</v>
+        <v>1.1288</v>
       </c>
       <c r="J303" t="n">
-        <v>27.2343</v>
+        <v>25.9624</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4223</v>
+        <v>0.5125</v>
       </c>
       <c r="J304" t="n">
-        <v>9.712899999999999</v>
+        <v>11.7875</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.16</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3466</v>
+        <v>0.4365</v>
       </c>
       <c r="J305" t="n">
-        <v>7.9718</v>
+        <v>10.0395</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0905</v>
       </c>
       <c r="J306" t="n">
-        <v>0.1932</v>
+        <v>2.0815</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0578</v>
+        <v>-0.0713</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.3294</v>
+        <v>-1.6399</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.3741</v>
+        <v>-2.9946</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3834</v>
+        <v>-0.2604</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.818199999999999</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4769</v>
+        <v>-0.3171</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.9687</v>
+        <v>-7.2933</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5342</v>
+        <v>-0.3549</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.2866</v>
+        <v>-8.162699999999999</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.6</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3591</v>
+        <v>1.2383</v>
       </c>
       <c r="J312" t="n">
-        <v>29.9002</v>
+        <v>27.2426</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0154</v>
+        <v>1.0256</v>
       </c>
       <c r="J313" t="n">
-        <v>22.3388</v>
+        <v>22.5632</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.41</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9717</v>
+        <v>0.9943</v>
       </c>
       <c r="J314" t="n">
-        <v>21.3774</v>
+        <v>21.8746</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.12</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2408</v>
+        <v>0.3293</v>
       </c>
       <c r="J315" t="n">
-        <v>5.2976</v>
+        <v>7.2446</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.06</v>
       </c>
       <c r="I316" t="n">
-        <v>0.0707</v>
+        <v>0.1546</v>
       </c>
       <c r="J316" t="n">
-        <v>1.5554</v>
+        <v>3.4012</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>0.0137</v>
+        <v>-0.0221</v>
       </c>
       <c r="J317" t="n">
-        <v>0.3014</v>
+        <v>-0.4862</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1024</v>
+        <v>-0.0992</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.2528</v>
+        <v>-2.1824</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2073</v>
+        <v>-0.1657</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.5606</v>
+        <v>-3.6454</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.7</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.469</v>
+        <v>-0.3102</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.318</v>
+        <v>-6.8244</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.659</v>
+        <v>-0.4417</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.498</v>
+        <v>-9.7174</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6345/event_6345_evp_summary.xlsx
+++ b/database/event/6345/event_6345_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5153</v>
+        <v>8.3491</v>
       </c>
       <c r="C2" t="n">
-        <v>3.055</v>
+        <v>2.9954</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2062</v>
+        <v>3.1765</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5153</v>
+        <v>8.3491</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1784</v>
+        <v>2.1583</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3368</v>
+        <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1784</v>
+        <v>2.1583</v>
       </c>
       <c r="I2" t="n">
-        <v>2.268</v>
+        <v>2.2139</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3368</v>
+        <v>6.7289</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>165</v>
       </c>
       <c r="M2" t="n">
-        <v>8.604800000000001</v>
+        <v>8.9428</v>
       </c>
       <c r="N2" t="n">
         <v>295</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3275</v>
+        <v>6.2734</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2701</v>
+        <v>2.2507</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2185</v>
+        <v>2.2316</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3275</v>
+        <v>6.2734</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1628</v>
+        <v>2.8716</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1647</v>
+        <v>3.4018</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5853</v>
+        <v>3.5602</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7327</v>
+        <v>3.6519</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1647</v>
+        <v>3.4018</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>6.897399999999999</v>
+        <v>7.0537</v>
       </c>
       <c r="N3" t="n">
         <v>331</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5367</v>
+        <v>5.9245</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9864</v>
+        <v>2.1255</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8615</v>
+        <v>2.0728</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5367</v>
+        <v>5.9245</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5306</v>
+        <v>0.5477</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0061</v>
+        <v>5.3768</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5306</v>
+        <v>0.5477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5524</v>
+        <v>0.5618</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0061</v>
+        <v>5.3768</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5585</v>
+        <v>5.9386</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1912</v>
+        <v>5.7836</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8625</v>
+        <v>2.075</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7056</v>
+        <v>2.0086</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1912</v>
+        <v>5.7836</v>
       </c>
       <c r="F5" t="n">
-        <v>0.824</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3672</v>
+        <v>4.892</v>
       </c>
       <c r="H5" t="n">
-        <v>0.824</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8579</v>
+        <v>0.9146</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3672</v>
+        <v>4.892</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>165</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2251</v>
+        <v>5.8066</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9055</v>
+        <v>4.9035</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7599</v>
+        <v>1.7592</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5766</v>
+        <v>1.608</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9055</v>
+        <v>4.9035</v>
       </c>
       <c r="F6" t="n">
-        <v>4.441</v>
+        <v>4.385</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4645</v>
+        <v>0.5185</v>
       </c>
       <c r="H6" t="n">
-        <v>10.1611</v>
+        <v>9.573499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2833</v>
+        <v>5.1696</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4645</v>
+        <v>0.5185</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7478</v>
+        <v>5.6881</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3048</v>
+        <v>3.2536</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1857</v>
+        <v>1.1673</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8539</v>
+        <v>0.8569</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3048</v>
+        <v>3.2536</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9683</v>
+        <v>2.8848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3365</v>
+        <v>0.3688</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9722</v>
+        <v>4.6238</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5853</v>
+        <v>2.4968</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3365</v>
+        <v>0.3688</v>
       </c>
       <c r="K7" t="n">
         <v>134</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9218</v>
+        <v>2.8656</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1161</v>
+        <v>3.0419</v>
       </c>
       <c r="C8" t="n">
-        <v>1.118</v>
+        <v>1.0913</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7687</v>
+        <v>0.7605</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1161</v>
+        <v>3.0419</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1356</v>
+        <v>3.0747</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0195</v>
+        <v>-0.0328</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5616</v>
+        <v>5.2503</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8918</v>
+        <v>2.8351</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0195</v>
+        <v>-0.0328</v>
       </c>
       <c r="K8" t="n">
         <v>148</v>
@@ -805,7 +805,7 @@
         <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8723</v>
+        <v>2.8023</v>
       </c>
       <c r="N8" t="n">
         <v>230</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8863</v>
+        <v>2.8531</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0355</v>
+        <v>1.0236</v>
       </c>
       <c r="D9" t="n">
-        <v>0.665</v>
+        <v>0.6746</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8863</v>
+        <v>2.8531</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6208</v>
+        <v>2.5515</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2655</v>
+        <v>0.3016</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7476</v>
+        <v>3.5241</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9486</v>
+        <v>1.903</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2655</v>
+        <v>0.3016</v>
       </c>
       <c r="K9" t="n">
         <v>148</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2141</v>
+        <v>2.2046</v>
       </c>
       <c r="N9" t="n">
         <v>230</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.759</v>
+        <v>2.8141</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9898</v>
+        <v>1.0096</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6075</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.759</v>
+        <v>2.8141</v>
       </c>
       <c r="F10" t="n">
-        <v>1.806</v>
+        <v>1.7506</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>1.0635</v>
       </c>
       <c r="H10" t="n">
-        <v>1.806</v>
+        <v>1.7506</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8803</v>
+        <v>1.7957</v>
       </c>
       <c r="J10" t="n">
-        <v>0.953</v>
+        <v>1.0635</v>
       </c>
       <c r="K10" t="n">
         <v>130</v>
@@ -897,7 +897,7 @@
         <v>165</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8333</v>
+        <v>2.8592</v>
       </c>
       <c r="N10" t="n">
         <v>295</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6949</v>
+        <v>2.5801</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9669</v>
+        <v>0.9257</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5786</v>
+        <v>0.5503</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6949</v>
+        <v>2.5801</v>
       </c>
       <c r="F11" t="n">
-        <v>2.641</v>
+        <v>2.5332</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0539</v>
+        <v>0.0469</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8188</v>
+        <v>3.4638</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9856</v>
+        <v>1.8704</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0539</v>
+        <v>0.0469</v>
       </c>
       <c r="K11" t="n">
         <v>134</v>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0395</v>
+        <v>1.9173</v>
       </c>
       <c r="N11" t="n">
         <v>215</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5565</v>
+        <v>2.4456</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9172</v>
+        <v>0.8774</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5161</v>
+        <v>0.4891</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5565</v>
+        <v>2.4456</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6916</v>
+        <v>2.5966</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1351</v>
+        <v>-0.151</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9973</v>
+        <v>3.673</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0784</v>
+        <v>1.9834</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1351</v>
+        <v>-0.151</v>
       </c>
       <c r="K12" t="n">
         <v>134</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9433</v>
+        <v>1.8324</v>
       </c>
       <c r="N12" t="n">
         <v>215</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9972</v>
+        <v>1.9314</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7165</v>
+        <v>0.6929</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2636</v>
+        <v>0.255</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9972</v>
+        <v>1.9314</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0942</v>
+        <v>2.0718</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.097</v>
+        <v>-0.1404</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0942</v>
+        <v>2.0718</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1803</v>
+        <v>2.1252</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.097</v>
+        <v>-0.1404</v>
       </c>
       <c r="K13" t="n">
         <v>118</v>
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0833</v>
+        <v>1.9848</v>
       </c>
       <c r="N13" t="n">
         <v>157</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.885</v>
+        <v>1.8393</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6763</v>
+        <v>0.6599</v>
       </c>
       <c r="D14" t="n">
-        <v>0.213</v>
+        <v>0.2131</v>
       </c>
       <c r="E14" t="n">
-        <v>1.885</v>
+        <v>1.8393</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9944</v>
+        <v>1.2473</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1094</v>
+        <v>0.592</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9944</v>
+        <v>1.2473</v>
       </c>
       <c r="I14" t="n">
-        <v>1.037</v>
+        <v>1.2794</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1094</v>
+        <v>0.592</v>
       </c>
       <c r="K14" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9276</v>
+        <v>1.8714</v>
       </c>
       <c r="N14" t="n">
-        <v>215</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6504</v>
+        <v>1.8166</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5921</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1071</v>
+        <v>0.2028</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6504</v>
+        <v>1.8166</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2818</v>
+        <v>1.9343</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3686</v>
+        <v>-0.1177</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2818</v>
+        <v>1.9343</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3345</v>
+        <v>1.0445</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3686</v>
+        <v>-0.1177</v>
       </c>
       <c r="K15" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L15" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7031</v>
+        <v>0.9268</v>
       </c>
       <c r="N15" t="n">
-        <v>331</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4585</v>
+        <v>1.5504</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5233</v>
+        <v>0.5562</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0204</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4585</v>
+        <v>1.5504</v>
       </c>
       <c r="F16" t="n">
-        <v>2.302</v>
+        <v>1.0473</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8435</v>
+        <v>0.5031</v>
       </c>
       <c r="H16" t="n">
-        <v>2.302</v>
+        <v>1.0473</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3967</v>
+        <v>1.0743</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8435</v>
+        <v>0.5031</v>
       </c>
       <c r="K16" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5532</v>
+        <v>1.5774</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4135</v>
+        <v>1.4655</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5071</v>
+        <v>0.5258</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001</v>
+        <v>0.0429</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4135</v>
+        <v>1.4655</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4541</v>
+        <v>1.4128</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0406</v>
+        <v>0.0527</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4541</v>
+        <v>1.4128</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5139</v>
+        <v>1.4492</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0406</v>
+        <v>0.0527</v>
       </c>
       <c r="K17" t="n">
         <v>142</v>
@@ -1219,7 +1219,7 @@
         <v>189</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4733</v>
+        <v>1.5019</v>
       </c>
       <c r="N17" t="n">
         <v>331</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2837</v>
+        <v>1.3862</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4606</v>
+        <v>0.4973</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0585</v>
+        <v>0.0068</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2837</v>
+        <v>1.3862</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0322</v>
+        <v>2.259</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2515</v>
+        <v>-0.8728</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0322</v>
+        <v>2.259</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0746</v>
+        <v>2.3172</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2515</v>
+        <v>-0.8728</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L18" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3261</v>
+        <v>1.4444</v>
       </c>
       <c r="N18" t="n">
-        <v>295</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0953</v>
+        <v>1.0794</v>
       </c>
       <c r="C19" t="n">
-        <v>0.393</v>
+        <v>0.3873</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1435</v>
+        <v>-0.1328</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0953</v>
+        <v>1.0794</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8715</v>
+        <v>0.7107</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7762</v>
+        <v>0.3687</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8715</v>
+        <v>0.7107</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9485</v>
+        <v>0.729</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7762</v>
+        <v>0.3687</v>
       </c>
       <c r="K19" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="L19" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1723</v>
+        <v>1.0977</v>
       </c>
       <c r="N19" t="n">
-        <v>157</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0887</v>
+        <v>1.0363</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3906</v>
+        <v>0.3718</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1465</v>
+        <v>-0.1525</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0887</v>
+        <v>1.0363</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0887</v>
+        <v>1.844</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.8077</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0887</v>
+        <v>1.844</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0887</v>
+        <v>1.8915</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.8077</v>
       </c>
       <c r="K20" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0887</v>
+        <v>1.0838</v>
       </c>
       <c r="N20" t="n">
-        <v>114</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0409</v>
+        <v>0.9977</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3734</v>
+        <v>0.3579</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1681</v>
+        <v>-0.17</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0409</v>
+        <v>0.9977</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2672</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8055</v>
+        <v>0.9977</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2672</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="L21" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0727</v>
+        <v>0.9977</v>
       </c>
       <c r="N21" t="n">
-        <v>331</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9821</v>
+        <v>0.9928</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3523</v>
+        <v>0.3562</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1946</v>
+        <v>-0.1723</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9821</v>
+        <v>0.9928</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8294</v>
+        <v>0.8297</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1527</v>
+        <v>0.1631</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8294</v>
+        <v>0.8297</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8294</v>
+        <v>0.8297</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1527</v>
+        <v>0.1631</v>
       </c>
       <c r="K22" t="n">
         <v>118</v>
@@ -1449,7 +1449,7 @@
         <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9821</v>
+        <v>0.9928</v>
       </c>
       <c r="N22" t="n">
         <v>180</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7844</v>
+        <v>0.7251</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2814</v>
+        <v>0.2601</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2839</v>
+        <v>-0.2941</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7844</v>
+        <v>0.7251</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8162</v>
+        <v>0.7251</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0318</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8162</v>
+        <v>0.7251</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4244</v>
+        <v>0.7251</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0318</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="L23" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3926</v>
+        <v>0.7251</v>
       </c>
       <c r="N23" t="n">
-        <v>230</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.6582</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2787</v>
+        <v>0.2361</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2874</v>
+        <v>-0.3246</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.6582</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.637</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.0212</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.637</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.0212</v>
       </c>
       <c r="K24" t="n">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.3652</v>
       </c>
       <c r="N24" t="n">
-        <v>114</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2071</v>
+        <v>0.1596</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3774</v>
+        <v>-0.4217</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5772</v>
+        <v>0.4448</v>
       </c>
       <c r="N25" t="n">
         <v>112</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4466</v>
+        <v>0.3761</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1602</v>
+        <v>0.1349</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4364</v>
+        <v>-0.453</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4466</v>
+        <v>0.3761</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9101</v>
+        <v>0.8789</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4635</v>
+        <v>-0.5028</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9101</v>
+        <v>0.8789</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4732</v>
+        <v>0.4746</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4635</v>
+        <v>-0.5028</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>81</v>
       </c>
       <c r="M26" t="n">
-        <v>0.009699999999999986</v>
+        <v>-0.0282</v>
       </c>
       <c r="N26" t="n">
         <v>215</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4246</v>
+        <v>0.3531</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1523</v>
+        <v>0.1267</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4463</v>
+        <v>-0.4635</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4246</v>
+        <v>0.3531</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8486</v>
+        <v>0.8092</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.424</v>
+        <v>-0.4561</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8486</v>
+        <v>0.8092</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8486</v>
+        <v>0.8092</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.424</v>
+        <v>-0.4561</v>
       </c>
       <c r="K27" t="n">
         <v>118</v>
@@ -1679,7 +1679,7 @@
         <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4246</v>
+        <v>0.3531</v>
       </c>
       <c r="N27" t="n">
         <v>180</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1279</v>
+        <v>0.1105</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4771</v>
+        <v>-0.4839</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3565</v>
+        <v>0.3081</v>
       </c>
       <c r="N28" t="n">
         <v>114</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1481</v>
+        <v>0.1615</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0531</v>
+        <v>0.0579</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5712</v>
+        <v>-0.5507</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1481</v>
+        <v>0.1615</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8571</v>
+        <v>0.9029</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.709</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8571</v>
+        <v>0.9029</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8924</v>
+        <v>0.9262</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.709</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>118</v>
@@ -1771,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1834</v>
+        <v>0.1848000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0287</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0103</v>
+        <v>-0.0237</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.651</v>
+        <v>-0.6543</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0287</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6279</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6566</v>
+        <v>-0.6956</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6279</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6566</v>
+        <v>-0.6956</v>
       </c>
       <c r="K30" t="n">
         <v>118</v>
@@ -1817,7 +1817,7 @@
         <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.002900000000000014</v>
+        <v>-0.04989999999999994</v>
       </c>
       <c r="N30" t="n">
         <v>157</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0396</v>
+        <v>-0.0993</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0142</v>
+        <v>-0.0356</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6559</v>
+        <v>-0.6694</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0396</v>
+        <v>-0.0993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1149</v>
+        <v>0.0813</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1545</v>
+        <v>-0.1806</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1149</v>
+        <v>0.0813</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1149</v>
+        <v>0.0813</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1545</v>
+        <v>-0.1806</v>
       </c>
       <c r="K31" t="n">
         <v>118</v>
@@ -1863,7 +1863,7 @@
         <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0396</v>
+        <v>-0.09930000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>180</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4484</v>
+        <v>-0.3673</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1609</v>
+        <v>-0.1318</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8404</v>
+        <v>-0.7914</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4484</v>
+        <v>-0.3673</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3998</v>
+        <v>1.422</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.8482</v>
+        <v>-1.7893</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3998</v>
+        <v>1.422</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4574</v>
+        <v>1.4586</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.8482</v>
+        <v>-1.7893</v>
       </c>
       <c r="K32" t="n">
         <v>142</v>
@@ -1909,7 +1909,7 @@
         <v>189</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3908</v>
+        <v>-0.3307</v>
       </c>
       <c r="N32" t="n">
         <v>331</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5682</v>
+        <v>-0.5964</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2039</v>
+        <v>-0.214</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8945</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5682</v>
+        <v>-0.5964</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.61</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0418</v>
+        <v>0.0301</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.61</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.61</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0418</v>
+        <v>0.0301</v>
       </c>
       <c r="K33" t="n">
         <v>118</v>
@@ -1955,7 +1955,7 @@
         <v>62</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5682</v>
+        <v>-0.5963999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>180</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3019</v>
+        <v>-0.318</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.018</v>
+        <v>-1.0277</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8416</v>
+        <v>-0.8864</v>
       </c>
       <c r="N34" t="n">
         <v>114</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3168</v>
+        <v>-0.3383</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0366</v>
+        <v>-1.0535</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8829</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>112</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9658</v>
+        <v>-1.0237</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3465</v>
+        <v>-0.3673</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.074</v>
+        <v>-1.0902</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9658</v>
+        <v>-1.0237</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4717</v>
+        <v>-0.498</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.4941</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4717</v>
+        <v>-0.498</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4717</v>
+        <v>-0.498</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4941</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>118</v>
@@ -2093,7 +2093,7 @@
         <v>62</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9658</v>
+        <v>-1.0237</v>
       </c>
       <c r="N36" t="n">
         <v>180</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3924</v>
+        <v>-0.4124</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1318</v>
+        <v>-1.1475</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0938</v>
+        <v>-1.1495</v>
       </c>
       <c r="N37" t="n">
         <v>114</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.418</v>
+        <v>-0.4375</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.164</v>
+        <v>-1.1793</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.165</v>
+        <v>-1.2194</v>
       </c>
       <c r="N38" t="n">
         <v>112</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5455</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3245</v>
+        <v>-1.3322</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5206</v>
+        <v>-1.5552</v>
       </c>
       <c r="N39" t="n">
         <v>112</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5635</v>
+        <v>-0.5764</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3471</v>
+        <v>-1.3555</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5706</v>
+        <v>-1.6065</v>
       </c>
       <c r="N40" t="n">
         <v>112</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8572</v>
+        <v>-1.6355</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6663</v>
+        <v>-0.5868</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4764</v>
+        <v>-1.3687</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8572</v>
+        <v>-1.6355</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1925</v>
+        <v>-1.9869</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3353</v>
+        <v>0.3514</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1925</v>
+        <v>-1.9869</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.14</v>
+        <v>-1.0729</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3353</v>
+        <v>0.3514</v>
       </c>
       <c r="K41" t="n">
         <v>148</v>
@@ -2323,7 +2323,7 @@
         <v>82</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.8047</v>
+        <v>-0.7215</v>
       </c>
       <c r="N41" t="n">
         <v>230</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1211</v>
+        <v>1.1086</v>
       </c>
       <c r="J2" t="n">
-        <v>26.9064</v>
+        <v>26.6064</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9143</v>
+        <v>0.8578</v>
       </c>
       <c r="J3" t="n">
-        <v>21.9432</v>
+        <v>20.5872</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8461</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>20.3064</v>
+        <v>19.1496</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4267</v>
+        <v>-0.4026</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.2408</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5377</v>
+        <v>-0.5034</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.9048</v>
+        <v>-12.0816</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5129</v>
+        <v>0.4952</v>
       </c>
       <c r="J7" t="n">
-        <v>12.3096</v>
+        <v>11.8848</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0177</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2544</v>
+        <v>-0.4248</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0915</v>
+        <v>-0.1051</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.196</v>
+        <v>-2.5224</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2174</v>
+        <v>-0.2334</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.2176</v>
+        <v>-5.6016</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4461</v>
+        <v>-0.4551</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.7064</v>
+        <v>-10.9224</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.89</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5432</v>
+        <v>1.6821</v>
       </c>
       <c r="J12" t="n">
-        <v>32.4072</v>
+        <v>35.3241</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2346</v>
+        <v>1.2888</v>
       </c>
       <c r="J13" t="n">
-        <v>25.9266</v>
+        <v>27.0648</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0348</v>
+        <v>0.9984</v>
       </c>
       <c r="J14" t="n">
-        <v>21.7308</v>
+        <v>20.9664</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.43</v>
       </c>
       <c r="I15" t="n">
-        <v>1.006</v>
+        <v>0.9626</v>
       </c>
       <c r="J15" t="n">
-        <v>21.126</v>
+        <v>20.2146</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0552</v>
+        <v>0.0929</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1592</v>
+        <v>1.9509</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1221</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.9383</v>
+        <v>-2.5641</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2182</v>
+        <v>-0.2446</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.5822</v>
+        <v>-5.1366</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.63</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3485</v>
+        <v>-0.3694</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.3185</v>
+        <v>-7.7574</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.543</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.1888</v>
+        <v>-11.403</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6093</v>
+        <v>-0.6135</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.7953</v>
+        <v>-12.8835</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5141</v>
+        <v>0.5683</v>
       </c>
       <c r="J22" t="n">
-        <v>14.9089</v>
+        <v>16.4807</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0091</v>
+        <v>0.0065</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2639</v>
+        <v>0.1885</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0948</v>
+        <v>-0.1075</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7492</v>
+        <v>-3.1175</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0948</v>
+        <v>-0.1075</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.7492</v>
+        <v>-3.1175</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4509</v>
+        <v>-0.4588</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.0761</v>
+        <v>-13.3052</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.849</v>
+        <v>0.9354</v>
       </c>
       <c r="J27" t="n">
-        <v>24.621</v>
+        <v>27.1266</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7441</v>
+        <v>0.8223</v>
       </c>
       <c r="J28" t="n">
-        <v>21.5789</v>
+        <v>23.8467</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3829</v>
+        <v>0.4133</v>
       </c>
       <c r="J29" t="n">
-        <v>11.1041</v>
+        <v>11.9857</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3068</v>
+        <v>-0.2921</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.8972</v>
+        <v>-8.4709</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3671</v>
+        <v>-0.3482</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.6459</v>
+        <v>-10.0978</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5785</v>
       </c>
       <c r="J32" t="n">
-        <v>12.1584</v>
+        <v>13.884</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.401</v>
+        <v>0.4528</v>
       </c>
       <c r="J33" t="n">
-        <v>9.624000000000001</v>
+        <v>10.8672</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3372</v>
+        <v>0.3582</v>
       </c>
       <c r="J34" t="n">
-        <v>8.0928</v>
+        <v>8.5968</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.131</v>
+        <v>-0.1387</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.144</v>
+        <v>-3.3288</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1425</v>
+        <v>-0.1505</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.42</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2943</v>
+        <v>0.2939</v>
       </c>
       <c r="J37" t="n">
-        <v>7.0632</v>
+        <v>7.0536</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1442</v>
+        <v>-0.1601</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.4608</v>
+        <v>-3.8424</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1545</v>
+        <v>-0.1707</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.708</v>
+        <v>-4.0968</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.175</v>
+        <v>-0.1915</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.2</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3321</v>
+        <v>-0.3462</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.9704</v>
+        <v>-8.3088</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J42" t="n">
-        <v>5.9827</v>
+        <v>6.1886</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0929</v>
+        <v>0.1007</v>
       </c>
       <c r="J43" t="n">
-        <v>2.6941</v>
+        <v>2.9203</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0929</v>
+        <v>0.1007</v>
       </c>
       <c r="J44" t="n">
-        <v>2.6941</v>
+        <v>2.9203</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0985</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.5375</v>
+        <v>-2.8565</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1446</v>
+        <v>-0.1577</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.1934</v>
+        <v>-4.5733</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7003</v>
+        <v>0.7699</v>
       </c>
       <c r="J47" t="n">
-        <v>20.3087</v>
+        <v>22.3271</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3623</v>
+        <v>0.3775</v>
       </c>
       <c r="J48" t="n">
-        <v>10.5067</v>
+        <v>10.9475</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3249</v>
+        <v>0.327</v>
       </c>
       <c r="J49" t="n">
-        <v>9.4221</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0167</v>
+        <v>-0.0114</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.4843</v>
+        <v>-0.3306</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6171</v>
+        <v>-0.5797</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.8959</v>
+        <v>-16.8113</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.5925</v>
+        <v>-1.9175</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.91</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1113</v>
+        <v>-0.1265</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.7825</v>
+        <v>-3.1625</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1331</v>
+        <v>-0.1489</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.3275</v>
+        <v>-3.7225</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.204</v>
+        <v>-0.2208</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.1</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2139</v>
+        <v>-0.2308</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.3475</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8296</v>
+        <v>0.9159</v>
       </c>
       <c r="J57" t="n">
-        <v>20.74</v>
+        <v>22.8975</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6589</v>
+        <v>0.7306</v>
       </c>
       <c r="J58" t="n">
-        <v>16.4725</v>
+        <v>18.265</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.25</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5366</v>
+        <v>0.5954</v>
       </c>
       <c r="J59" t="n">
-        <v>13.415</v>
+        <v>14.885</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1197</v>
+        <v>0.1381</v>
       </c>
       <c r="J60" t="n">
-        <v>2.9925</v>
+        <v>3.4525</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4317</v>
+        <v>-0.4061</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.7925</v>
+        <v>-10.1525</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.388</v>
+        <v>0.4331</v>
       </c>
       <c r="J62" t="n">
-        <v>11.64</v>
+        <v>12.993</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2276</v>
+        <v>0.2436</v>
       </c>
       <c r="J63" t="n">
-        <v>6.828</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1617</v>
+        <v>0.1773</v>
       </c>
       <c r="J64" t="n">
-        <v>4.851</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1185</v>
+        <v>0.1333</v>
       </c>
       <c r="J65" t="n">
-        <v>3.555</v>
+        <v>3.999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1119</v>
+        <v>-0.1208</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.357</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5016</v>
+        <v>0.5596</v>
       </c>
       <c r="J67" t="n">
-        <v>15.048</v>
+        <v>16.788</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I68" t="n">
-        <v>0.236</v>
+        <v>0.2438</v>
       </c>
       <c r="J68" t="n">
-        <v>7.08</v>
+        <v>7.314</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0493</v>
+        <v>-0.0577</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.479</v>
+        <v>-1.731</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2481</v>
+        <v>-0.2616</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.443</v>
+        <v>-7.848</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.373</v>
+        <v>-0.3833</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.19</v>
+        <v>-11.499</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>2.1216</v>
+        <v>2.1996</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.014</v>
+        <v>-0.0202</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.364</v>
+        <v>-0.5252</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1466</v>
+        <v>-1.3962</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1587</v>
+        <v>-0.1738</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.1262</v>
+        <v>-4.5188</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2403</v>
+        <v>-0.2555</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.2478</v>
+        <v>-6.643</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.98</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4491</v>
+        <v>1.5707</v>
       </c>
       <c r="J77" t="n">
-        <v>37.6766</v>
+        <v>40.8382</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8879</v>
+        <v>0.9796</v>
       </c>
       <c r="J78" t="n">
-        <v>23.0854</v>
+        <v>25.4696</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.38</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7075</v>
+        <v>0.7847</v>
       </c>
       <c r="J79" t="n">
-        <v>18.395</v>
+        <v>20.4022</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.9051</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-23.5326</v>
+        <v>-21.5046</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.52</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3485</v>
+        <v>-1.2097</v>
       </c>
       <c r="J81" t="n">
-        <v>-35.061</v>
+        <v>-31.4522</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.44</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7954</v>
+        <v>0.8781</v>
       </c>
       <c r="J82" t="n">
-        <v>20.6804</v>
+        <v>22.8306</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7163</v>
+        <v>0.7923</v>
       </c>
       <c r="J83" t="n">
-        <v>18.6238</v>
+        <v>20.5998</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.31</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6221</v>
+        <v>0.6893</v>
       </c>
       <c r="J84" t="n">
-        <v>16.1746</v>
+        <v>17.9218</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3979</v>
+        <v>-0.3762</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.3454</v>
+        <v>-9.7812</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5105</v>
+        <v>-0.4788</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.273</v>
+        <v>-12.4488</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0327</v>
+        <v>0.0236</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8502</v>
+        <v>0.6136</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0484</v>
+        <v>-0.0612</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.2584</v>
+        <v>-1.5912</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.232</v>
+        <v>-0.2491</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.032</v>
+        <v>-6.4766</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.232</v>
+        <v>-0.2491</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.032</v>
+        <v>-6.4766</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2516</v>
+        <v>-0.2684</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.5416</v>
+        <v>-6.9784</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8786</v>
+        <v>0.9665</v>
       </c>
       <c r="J92" t="n">
-        <v>31.6296</v>
+        <v>34.794</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.48</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8526</v>
+        <v>0.9387</v>
       </c>
       <c r="J93" t="n">
-        <v>30.6936</v>
+        <v>33.7932</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.24</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5286</v>
+        <v>0.585</v>
       </c>
       <c r="J94" t="n">
-        <v>19.0296</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3928</v>
+        <v>-0.3726</v>
       </c>
       <c r="J95" t="n">
-        <v>-14.1408</v>
+        <v>-13.4136</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9875</v>
+        <v>-0.9012</v>
       </c>
       <c r="J96" t="n">
-        <v>-35.55</v>
+        <v>-32.4432</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3847</v>
+        <v>0.4122</v>
       </c>
       <c r="J97" t="n">
-        <v>13.8492</v>
+        <v>14.8392</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0091</v>
+        <v>0.0065</v>
       </c>
       <c r="J98" t="n">
-        <v>0.3276</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1061</v>
+        <v>-0.1194</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.8196</v>
+        <v>-4.2984</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.192</v>
+        <v>-0.207</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.912</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2425</v>
+        <v>-0.2573</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.73</v>
+        <v>-9.2628</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.01</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0883</v>
+        <v>0.0801</v>
       </c>
       <c r="J102" t="n">
-        <v>1.9426</v>
+        <v>1.7622</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1887</v>
+        <v>-0.2069</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.1514</v>
+        <v>-4.5518</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2366</v>
+        <v>-0.2547</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.2052</v>
+        <v>-5.6034</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2462</v>
+        <v>-0.2643</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.4164</v>
+        <v>-5.8146</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3038</v>
+        <v>-0.3205</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.6836</v>
+        <v>-7.051</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.107</v>
+        <v>1.2176</v>
       </c>
       <c r="J107" t="n">
-        <v>24.354</v>
+        <v>26.7872</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.56</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9143</v>
+        <v>1.0124</v>
       </c>
       <c r="J108" t="n">
-        <v>20.1146</v>
+        <v>22.2728</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.44</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7661</v>
+        <v>0.8524</v>
       </c>
       <c r="J109" t="n">
-        <v>16.8542</v>
+        <v>18.7528</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1209</v>
+        <v>0.1476</v>
       </c>
       <c r="J110" t="n">
-        <v>2.6598</v>
+        <v>3.2472</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4628</v>
+        <v>-0.428</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.1816</v>
+        <v>-9.416</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.75</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1853</v>
+        <v>-0.2205</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.1501</v>
+        <v>-3.7485</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.53</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.42</v>
+        <v>-0.4409</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.14</v>
+        <v>-7.4953</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5203</v>
+        <v>-0.5345</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.8451</v>
+        <v>-9.086499999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.41</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.53</v>
+        <v>-0.5434</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.01</v>
+        <v>-9.2378</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5397</v>
+        <v>-0.5523</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.174899999999999</v>
+        <v>-9.389099999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.29</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6615</v>
+        <v>1.8104</v>
       </c>
       <c r="J117" t="n">
-        <v>28.2455</v>
+        <v>30.7768</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8974</v>
+        <v>1.0028</v>
       </c>
       <c r="J118" t="n">
-        <v>15.2558</v>
+        <v>17.0476</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.55</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8626</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>14.6642</v>
+        <v>16.4084</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.55</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8626</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>14.6642</v>
+        <v>16.4084</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.45</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7427</v>
+        <v>0.835</v>
       </c>
       <c r="J121" t="n">
-        <v>12.6259</v>
+        <v>14.195</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1846</v>
+        <v>1.1448</v>
       </c>
       <c r="J122" t="n">
-        <v>34.3534</v>
+        <v>33.1992</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5598</v>
+        <v>0.5397</v>
       </c>
       <c r="J123" t="n">
-        <v>16.2342</v>
+        <v>15.6513</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2395</v>
+        <v>0.2456</v>
       </c>
       <c r="J124" t="n">
-        <v>6.9455</v>
+        <v>7.1224</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3165</v>
+        <v>-0.306</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.1785</v>
+        <v>-8.874000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6997</v>
+        <v>-0.652</v>
       </c>
       <c r="J126" t="n">
-        <v>-20.2913</v>
+        <v>-18.908</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5184</v>
+        <v>0.5059</v>
       </c>
       <c r="J127" t="n">
-        <v>15.0336</v>
+        <v>14.6711</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4268</v>
+        <v>0.4214</v>
       </c>
       <c r="J128" t="n">
-        <v>12.3772</v>
+        <v>12.2206</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.098</v>
+        <v>-0.1099</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.842</v>
+        <v>-3.1871</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.85</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.3824</v>
+        <v>-5.7913</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3434</v>
+        <v>-0.3551</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.958600000000001</v>
+        <v>-10.2979</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0519</v>
+        <v>1.0084</v>
       </c>
       <c r="J132" t="n">
-        <v>26.2975</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9929</v>
+        <v>0.9418</v>
       </c>
       <c r="J133" t="n">
-        <v>24.8225</v>
+        <v>23.545</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7237</v>
+        <v>0.6962</v>
       </c>
       <c r="J134" t="n">
-        <v>18.0925</v>
+        <v>17.405</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7009</v>
+        <v>0.676</v>
       </c>
       <c r="J135" t="n">
-        <v>17.5225</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.25</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6349</v>
       </c>
       <c r="J136" t="n">
-        <v>16.3675</v>
+        <v>15.8725</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2674</v>
+        <v>0.2581</v>
       </c>
       <c r="J137" t="n">
-        <v>6.685</v>
+        <v>6.4525</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2212</v>
+        <v>0.2135</v>
       </c>
       <c r="J138" t="n">
-        <v>5.53</v>
+        <v>5.3375</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.71</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3038</v>
+        <v>-0.3205</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.595</v>
+        <v>-8.012499999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.67</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3418</v>
+        <v>-0.3572</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.545</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4262</v>
+        <v>-0.4378</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.655</v>
+        <v>-10.945</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.74</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4348</v>
+        <v>1.4169</v>
       </c>
       <c r="J142" t="n">
-        <v>37.3048</v>
+        <v>36.8394</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.719</v>
+        <v>0.6883</v>
       </c>
       <c r="J143" t="n">
-        <v>18.694</v>
+        <v>17.8958</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4063</v>
+        <v>0.4066</v>
       </c>
       <c r="J144" t="n">
-        <v>10.5638</v>
+        <v>10.5716</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.079</v>
+        <v>0.1003</v>
       </c>
       <c r="J145" t="n">
-        <v>2.054</v>
+        <v>2.6078</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3194</v>
+        <v>-0.301</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.304399999999999</v>
+        <v>-7.826</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3698</v>
+        <v>0.3562</v>
       </c>
       <c r="J147" t="n">
-        <v>9.614800000000001</v>
+        <v>9.261200000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1918</v>
+        <v>0.1861</v>
       </c>
       <c r="J148" t="n">
-        <v>4.9868</v>
+        <v>4.8386</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2478</v>
+        <v>-0.2654</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.4428</v>
+        <v>-6.9004</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.334</v>
+        <v>-0.3494</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.683999999999999</v>
+        <v>-9.0844</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.474</v>
+        <v>-0.4829</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.324</v>
+        <v>-12.5554</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8731</v>
+        <v>0.8207</v>
       </c>
       <c r="J152" t="n">
-        <v>20.9544</v>
+        <v>19.6968</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.21</v>
       </c>
       <c r="I153" t="n">
-        <v>0.59</v>
+        <v>0.5707</v>
       </c>
       <c r="J153" t="n">
-        <v>14.16</v>
+        <v>13.6968</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4436</v>
+        <v>0.438</v>
       </c>
       <c r="J154" t="n">
-        <v>10.6464</v>
+        <v>10.512</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3103</v>
+        <v>0.3156</v>
       </c>
       <c r="J155" t="n">
-        <v>7.4472</v>
+        <v>7.5744</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.04</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1277</v>
+        <v>0.1437</v>
       </c>
       <c r="J156" t="n">
-        <v>3.0648</v>
+        <v>3.4488</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0709</v>
+        <v>-0.0858</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.7016</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1181</v>
+        <v>-0.1346</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.8344</v>
+        <v>-3.2304</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.14</v>
+        <v>-0.157</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.36</v>
+        <v>-3.768</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1807</v>
+        <v>-0.1983</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.3368</v>
+        <v>-4.7592</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3638</v>
+        <v>-0.3778</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.731199999999999</v>
+        <v>-9.0672</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5956</v>
+        <v>0.6019</v>
       </c>
       <c r="J162" t="n">
-        <v>13.6988</v>
+        <v>13.8437</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4219</v>
+        <v>0.4373</v>
       </c>
       <c r="J163" t="n">
-        <v>9.7037</v>
+        <v>10.0579</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.29</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3782</v>
+        <v>0.3951</v>
       </c>
       <c r="J164" t="n">
-        <v>8.698600000000001</v>
+        <v>9.087300000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2606</v>
+        <v>0.2805</v>
       </c>
       <c r="J165" t="n">
-        <v>5.9938</v>
+        <v>6.4515</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2353</v>
+        <v>0.2556</v>
       </c>
       <c r="J166" t="n">
-        <v>5.4119</v>
+        <v>5.8788</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.21</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3991</v>
+        <v>0.3903</v>
       </c>
       <c r="J167" t="n">
-        <v>9.1793</v>
+        <v>8.976900000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1031</v>
+        <v>0.1027</v>
       </c>
       <c r="J168" t="n">
-        <v>2.3713</v>
+        <v>2.3621</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2789</v>
+        <v>-0.2955</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.4147</v>
+        <v>-6.7965</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3834</v>
+        <v>-0.3964</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.818199999999999</v>
+        <v>-9.1172</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3834</v>
+        <v>-0.3964</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.818199999999999</v>
+        <v>-9.1172</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5406</v>
+        <v>0.5288</v>
       </c>
       <c r="J172" t="n">
-        <v>15.6774</v>
+        <v>15.3352</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3777</v>
+        <v>0.378</v>
       </c>
       <c r="J173" t="n">
-        <v>10.9533</v>
+        <v>10.962</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.12</v>
       </c>
       <c r="I174" t="n">
-        <v>0.282</v>
+        <v>0.2876</v>
       </c>
       <c r="J174" t="n">
-        <v>8.178000000000001</v>
+        <v>8.340400000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1795</v>
+        <v>-0.1925</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.2055</v>
+        <v>-5.5825</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3571</v>
+        <v>-0.3675</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.3559</v>
+        <v>-10.6575</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8558</v>
+        <v>0.8006</v>
       </c>
       <c r="J177" t="n">
-        <v>24.8182</v>
+        <v>23.2174</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6302</v>
       </c>
       <c r="J178" t="n">
-        <v>19.1922</v>
+        <v>18.2758</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2973</v>
+        <v>0.2998</v>
       </c>
       <c r="J179" t="n">
-        <v>8.621700000000001</v>
+        <v>8.6942</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1527</v>
+        <v>-0.1511</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.4283</v>
+        <v>-4.3819</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5409</v>
+        <v>-0.511</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.6861</v>
+        <v>-14.819</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2959</v>
+        <v>-0.3183</v>
       </c>
       <c r="J182" t="n">
-        <v>-6.2139</v>
+        <v>-6.6843</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.67</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3152</v>
+        <v>-0.3367</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.6192</v>
+        <v>-7.0707</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.62</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3599</v>
+        <v>-0.3798</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.5579</v>
+        <v>-7.9758</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.59</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3868</v>
+        <v>-0.4056</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.1228</v>
+        <v>-8.5176</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.396</v>
+        <v>-0.4143</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.7003</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.02</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6885</v>
+        <v>1.6943</v>
       </c>
       <c r="J187" t="n">
-        <v>35.4585</v>
+        <v>35.5803</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>2.02</v>
       </c>
       <c r="I188" t="n">
-        <v>1.6885</v>
+        <v>1.6943</v>
       </c>
       <c r="J188" t="n">
-        <v>35.4585</v>
+        <v>35.5803</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.3</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7389</v>
+        <v>0.7155</v>
       </c>
       <c r="J189" t="n">
-        <v>15.5169</v>
+        <v>15.0255</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.452</v>
+        <v>0.4601</v>
       </c>
       <c r="J190" t="n">
-        <v>9.492000000000001</v>
+        <v>9.662100000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.91</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4357</v>
+        <v>-0.3965</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.149699999999999</v>
+        <v>-8.326499999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4479</v>
+        <v>0.3922</v>
       </c>
       <c r="J192" t="n">
-        <v>8.5101</v>
+        <v>7.4518</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3721</v>
+        <v>-0.3927</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.0699</v>
+        <v>-7.4613</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.5</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4622</v>
+        <v>-0.4779</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.7818</v>
+        <v>-9.0801</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5095</v>
+        <v>-0.522</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.6805</v>
+        <v>-9.917999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6539</v>
+        <v>-0.6548</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.4241</v>
+        <v>-12.4412</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.81</v>
       </c>
       <c r="I197" t="n">
-        <v>1.4518</v>
+        <v>1.4459</v>
       </c>
       <c r="J197" t="n">
-        <v>27.5842</v>
+        <v>27.4721</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.7</v>
       </c>
       <c r="I198" t="n">
-        <v>1.3262</v>
+        <v>1.3127</v>
       </c>
       <c r="J198" t="n">
-        <v>25.1978</v>
+        <v>24.9413</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.67</v>
       </c>
       <c r="I199" t="n">
-        <v>1.2917</v>
+        <v>1.2759</v>
       </c>
       <c r="J199" t="n">
-        <v>24.5423</v>
+        <v>24.2421</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.22</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5481</v>
       </c>
       <c r="J200" t="n">
-        <v>10.4481</v>
+        <v>10.4139</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1189</v>
+        <v>0.154</v>
       </c>
       <c r="J201" t="n">
-        <v>2.2591</v>
+        <v>2.926</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.72</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8818</v>
+        <v>0.8601</v>
       </c>
       <c r="J202" t="n">
-        <v>24.6904</v>
+        <v>24.0828</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0521</v>
+        <v>0.0644</v>
       </c>
       <c r="J203" t="n">
-        <v>1.4588</v>
+        <v>1.8032</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.02</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0335</v>
+        <v>0.0444</v>
       </c>
       <c r="J204" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.2432</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0888</v>
+        <v>-0.096</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.4864</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1477</v>
+        <v>-0.1574</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.1356</v>
+        <v>-4.4072</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3923</v>
+        <v>0.393</v>
       </c>
       <c r="J207" t="n">
-        <v>10.9844</v>
+        <v>11.004</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3647</v>
+        <v>0.3669</v>
       </c>
       <c r="J208" t="n">
-        <v>10.2116</v>
+        <v>10.2732</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0708</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>1.9824</v>
+        <v>2.2036</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2878</v>
+        <v>-0.3006</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.058400000000001</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2975</v>
+        <v>-0.3101</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.33</v>
+        <v>-8.6828</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.84</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1283</v>
+        <v>-0.1574</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.566</v>
+        <v>-3.148</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.74</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2395</v>
+        <v>-0.2651</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.79</v>
+        <v>-5.302</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4106</v>
+        <v>-0.4287</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.212</v>
+        <v>-8.574</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4198</v>
+        <v>-0.4374</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.396000000000001</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.35</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6093</v>
+        <v>-0.6135</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.186</v>
+        <v>-12.27</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4013</v>
+        <v>1.3893</v>
       </c>
       <c r="J217" t="n">
-        <v>28.026</v>
+        <v>27.786</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1285</v>
+        <v>1.0979</v>
       </c>
       <c r="J218" t="n">
-        <v>22.57</v>
+        <v>21.958</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.5</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1044</v>
+        <v>1.0715</v>
       </c>
       <c r="J219" t="n">
-        <v>22.088</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5205</v>
+        <v>0.5179</v>
       </c>
       <c r="J220" t="n">
-        <v>10.41</v>
+        <v>10.358</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.02</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0014</v>
+        <v>0.0354</v>
       </c>
       <c r="J221" t="n">
-        <v>0.028</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4656</v>
+        <v>0.453</v>
       </c>
       <c r="J222" t="n">
-        <v>16.296</v>
+        <v>15.855</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4656</v>
+        <v>0.453</v>
       </c>
       <c r="J223" t="n">
-        <v>16.296</v>
+        <v>15.855</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0814</v>
+        <v>0.0912</v>
       </c>
       <c r="J224" t="n">
-        <v>2.849</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0814</v>
+        <v>0.0912</v>
       </c>
       <c r="J225" t="n">
-        <v>2.849</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1092</v>
+        <v>-0.1102</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.822</v>
+        <v>-3.857</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6362</v>
+        <v>0.6173</v>
       </c>
       <c r="J227" t="n">
-        <v>22.267</v>
+        <v>21.6055</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6362</v>
+        <v>0.6173</v>
       </c>
       <c r="J228" t="n">
-        <v>22.267</v>
+        <v>21.6055</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.96</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0674</v>
+        <v>-0.0757</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.359</v>
+        <v>-2.6495</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.83</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2134</v>
+        <v>-0.2259</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.469</v>
+        <v>-7.9065</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2637</v>
+        <v>-0.2758</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.2295</v>
+        <v>-9.653</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2908</v>
+        <v>0.2881</v>
       </c>
       <c r="J232" t="n">
-        <v>8.433199999999999</v>
+        <v>8.354900000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1649</v>
+        <v>0.1691</v>
       </c>
       <c r="J233" t="n">
-        <v>4.7821</v>
+        <v>4.9039</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0538</v>
+        <v>0.059</v>
       </c>
       <c r="J234" t="n">
-        <v>1.5602</v>
+        <v>1.711</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2285</v>
+        <v>-0.2301</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.6265</v>
+        <v>-6.6729</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.92</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2896</v>
+        <v>-0.2873</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.398400000000001</v>
+        <v>-8.3317</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8403</v>
+        <v>0.8028</v>
       </c>
       <c r="J237" t="n">
-        <v>24.3687</v>
+        <v>23.2812</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.3</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5924</v>
+        <v>0.5792</v>
       </c>
       <c r="J238" t="n">
-        <v>17.1796</v>
+        <v>16.7968</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.95</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0833</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.4157</v>
+        <v>-2.6622</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1077</v>
+        <v>-0.1175</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.1233</v>
+        <v>-3.4075</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3154</v>
+        <v>-0.326</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.146599999999999</v>
+        <v>-9.454000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6508</v>
+        <v>0.6531</v>
       </c>
       <c r="J242" t="n">
-        <v>14.9684</v>
+        <v>15.0213</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>13.2503</v>
+        <v>13.4136</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2107</v>
+        <v>0.231</v>
       </c>
       <c r="J244" t="n">
-        <v>4.8461</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2107</v>
+        <v>0.231</v>
       </c>
       <c r="J245" t="n">
-        <v>4.8461</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.1</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1424</v>
+        <v>0.1629</v>
       </c>
       <c r="J246" t="n">
-        <v>3.2752</v>
+        <v>3.7467</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1725</v>
+        <v>0.174</v>
       </c>
       <c r="J247" t="n">
-        <v>3.9675</v>
+        <v>4.002</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.06</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1549</v>
+        <v>0.1565</v>
       </c>
       <c r="J248" t="n">
-        <v>3.5627</v>
+        <v>3.5995</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2125</v>
+        <v>-0.2297</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.8875</v>
+        <v>-5.2831</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2519</v>
+        <v>-0.2686</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.7937</v>
+        <v>-6.1778</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4042</v>
+        <v>-0.4159</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.2966</v>
+        <v>-9.5657</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.17</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3931</v>
+        <v>0.3893</v>
       </c>
       <c r="J252" t="n">
-        <v>11.0068</v>
+        <v>10.9004</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3547</v>
+        <v>0.3533</v>
       </c>
       <c r="J253" t="n">
-        <v>9.9316</v>
+        <v>9.8924</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0605</v>
+        <v>-0.0704</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.694</v>
+        <v>-1.9712</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0838</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.0412</v>
+        <v>-2.3464</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4166</v>
+        <v>-0.4257</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.6648</v>
+        <v>-11.9196</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7483</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J257" t="n">
-        <v>20.9524</v>
+        <v>19.7148</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5981</v>
+        <v>0.5713</v>
       </c>
       <c r="J258" t="n">
-        <v>16.7468</v>
+        <v>15.9964</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.15</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4681</v>
+        <v>0.4547</v>
       </c>
       <c r="J259" t="n">
-        <v>13.1068</v>
+        <v>12.7316</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1071</v>
+        <v>-0.1087</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.9988</v>
+        <v>-3.0436</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.914</v>
+        <v>-0.8414</v>
       </c>
       <c r="J261" t="n">
-        <v>-25.592</v>
+        <v>-23.5592</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.22</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4941</v>
+        <v>0.4814</v>
       </c>
       <c r="J262" t="n">
-        <v>14.3289</v>
+        <v>13.9606</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.01</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0474</v>
+        <v>0.0503</v>
       </c>
       <c r="J263" t="n">
-        <v>1.3746</v>
+        <v>1.4587</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0164</v>
+        <v>-0.0221</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.4756</v>
+        <v>-0.6409</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2724</v>
+        <v>-0.2865</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.8996</v>
+        <v>-8.3085</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2724</v>
+        <v>-0.2865</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.8996</v>
+        <v>-8.3085</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.42</v>
       </c>
       <c r="I267" t="n">
-        <v>1.034</v>
+        <v>0.9819</v>
       </c>
       <c r="J267" t="n">
-        <v>29.986</v>
+        <v>28.4751</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.24</v>
       </c>
       <c r="I268" t="n">
-        <v>0.652</v>
+        <v>0.6282</v>
       </c>
       <c r="J268" t="n">
-        <v>18.908</v>
+        <v>18.2178</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5445</v>
       </c>
       <c r="J269" t="n">
-        <v>16.211</v>
+        <v>15.7905</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3281</v>
+        <v>0.3344</v>
       </c>
       <c r="J270" t="n">
-        <v>9.514900000000001</v>
+        <v>9.6976</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.08</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2424</v>
+        <v>0.255</v>
       </c>
       <c r="J271" t="n">
-        <v>7.0296</v>
+        <v>7.395</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.38</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6162</v>
+        <v>0.5944</v>
       </c>
       <c r="J272" t="n">
-        <v>16.0212</v>
+        <v>15.4544</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3801</v>
+        <v>0.3759</v>
       </c>
       <c r="J273" t="n">
-        <v>9.8826</v>
+        <v>9.773400000000001</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.74</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2855</v>
+        <v>-0.3007</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.423</v>
+        <v>-7.8182</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.71</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3144</v>
+        <v>-0.3287</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.1744</v>
+        <v>-8.546200000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.45</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5543</v>
+        <v>-0.5573</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.4118</v>
+        <v>-14.4898</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.64</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7867</v>
+        <v>0.7743</v>
       </c>
       <c r="J277" t="n">
-        <v>20.4542</v>
+        <v>20.1318</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5556</v>
+        <v>0.5599</v>
       </c>
       <c r="J278" t="n">
-        <v>14.4456</v>
+        <v>14.5574</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0142</v>
+        <v>-0.0109</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.3692</v>
+        <v>-0.2834</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1835</v>
+        <v>-0.1932</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.771</v>
+        <v>-5.0232</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2252</v>
+        <v>-0.2352</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.8552</v>
+        <v>-6.1152</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3098</v>
+        <v>1.2809</v>
       </c>
       <c r="J282" t="n">
-        <v>31.4352</v>
+        <v>30.7416</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8336</v>
+        <v>0.785</v>
       </c>
       <c r="J283" t="n">
-        <v>20.0064</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.25</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6916</v>
+        <v>0.6602</v>
       </c>
       <c r="J284" t="n">
-        <v>16.5984</v>
+        <v>15.8448</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5295</v>
+        <v>-0.4976</v>
       </c>
       <c r="J285" t="n">
-        <v>-12.708</v>
+        <v>-11.9424</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.7</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.9122</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-21.8928</v>
+        <v>-20.0688</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8275</v>
+        <v>0.7781</v>
       </c>
       <c r="J287" t="n">
-        <v>19.86</v>
+        <v>18.6744</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.89</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1341</v>
+        <v>-0.1497</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.2184</v>
+        <v>-3.5928</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2157</v>
+        <v>-0.2321</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.1768</v>
+        <v>-5.5704</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.4144</v>
+        <v>-5.808</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4536</v>
+        <v>-0.4625</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.8864</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.59</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2261</v>
+        <v>1.2002</v>
       </c>
       <c r="J292" t="n">
-        <v>30.6525</v>
+        <v>30.005</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1033</v>
+        <v>1.068</v>
       </c>
       <c r="J293" t="n">
-        <v>27.5825</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9587</v>
+        <v>0.9067</v>
       </c>
       <c r="J294" t="n">
-        <v>23.9675</v>
+        <v>22.6675</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.35</v>
       </c>
       <c r="I295" t="n">
-        <v>0.877</v>
+        <v>0.8317</v>
       </c>
       <c r="J295" t="n">
-        <v>21.925</v>
+        <v>20.7925</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7024</v>
+        <v>-0.6446</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.56</v>
+        <v>-16.115</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2231</v>
+        <v>0.2092</v>
       </c>
       <c r="J297" t="n">
-        <v>5.5775</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2408</v>
+        <v>-0.2601</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.02</v>
+        <v>-6.5025</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.74</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2683</v>
+        <v>-0.2874</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.7075</v>
+        <v>-7.185</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.64</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3625</v>
+        <v>-0.3784</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.0625</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3625</v>
+        <v>-0.3784</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.0625</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.7</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3597</v>
+        <v>1.3422</v>
       </c>
       <c r="J302" t="n">
-        <v>31.2731</v>
+        <v>30.8706</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1288</v>
+        <v>1.0956</v>
       </c>
       <c r="J303" t="n">
-        <v>25.9624</v>
+        <v>25.1988</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5125</v>
+        <v>0.5073</v>
       </c>
       <c r="J304" t="n">
-        <v>11.7875</v>
+        <v>11.6679</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.16</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4365</v>
+        <v>0.4388</v>
       </c>
       <c r="J305" t="n">
-        <v>10.0395</v>
+        <v>10.0924</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.0905</v>
+        <v>0.1177</v>
       </c>
       <c r="J306" t="n">
-        <v>2.0815</v>
+        <v>2.7071</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0713</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.6399</v>
+        <v>-2.0562</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1302</v>
+        <v>-0.1494</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.9946</v>
+        <v>-3.4362</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2604</v>
+        <v>-0.2792</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.9892</v>
+        <v>-6.4216</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3171</v>
+        <v>-0.3345</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.2933</v>
+        <v>-7.6935</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3549</v>
+        <v>-0.3708</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.162699999999999</v>
+        <v>-8.5284</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.6</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2383</v>
+        <v>1.2132</v>
       </c>
       <c r="J312" t="n">
-        <v>27.2426</v>
+        <v>26.6904</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0256</v>
+        <v>0.9774</v>
       </c>
       <c r="J313" t="n">
-        <v>22.5632</v>
+        <v>21.5028</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.41</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9943</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>21.8746</v>
+        <v>20.746</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.12</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3293</v>
+        <v>0.3414</v>
       </c>
       <c r="J315" t="n">
-        <v>7.2446</v>
+        <v>7.5108</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.06</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1546</v>
+        <v>0.1791</v>
       </c>
       <c r="J316" t="n">
-        <v>3.4012</v>
+        <v>3.9402</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0221</v>
+        <v>-0.0366</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.4862</v>
+        <v>-0.8052</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0992</v>
+        <v>-0.1171</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.1824</v>
+        <v>-2.5762</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1657</v>
+        <v>-0.1844</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.6454</v>
+        <v>-4.0568</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.7</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3102</v>
+        <v>-0.3273</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.8244</v>
+        <v>-7.2006</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4417</v>
+        <v>-0.453</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.7174</v>
+        <v>-9.965999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6345/event_6345_evp_summary.xlsx
+++ b/database/event/6345/event_6345_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3491</v>
+        <v>8.317500000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9954</v>
+        <v>2.9841</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1765</v>
+        <v>3.1832</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3491</v>
+        <v>8.317500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1583</v>
+        <v>2.1108</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1583</v>
+        <v>2.1108</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2139</v>
+        <v>2.1672</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7289</v>
+        <v>6.7515</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>165</v>
       </c>
       <c r="M2" t="n">
-        <v>8.9428</v>
+        <v>8.918699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>295</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2734</v>
+        <v>6.1405</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2507</v>
+        <v>2.203</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2316</v>
+        <v>2.1915</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2734</v>
+        <v>6.1405</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8716</v>
+        <v>2.8171</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4018</v>
+        <v>3.3235</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5602</v>
+        <v>3.5058</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6519</v>
+        <v>3.5995</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4018</v>
+        <v>3.3235</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0537</v>
+        <v>6.923</v>
       </c>
       <c r="N3" t="n">
         <v>331</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9245</v>
+        <v>5.8782</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1255</v>
+        <v>2.1089</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0728</v>
+        <v>2.072</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9245</v>
+        <v>5.8782</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5477</v>
+        <v>0.4992</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3768</v>
+        <v>5.379</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5477</v>
+        <v>0.4992</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5618</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3768</v>
+        <v>5.379</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9386</v>
+        <v>5.8916</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7836</v>
+        <v>5.7586</v>
       </c>
       <c r="C5" t="n">
-        <v>2.075</v>
+        <v>2.066</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0086</v>
+        <v>2.0175</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7836</v>
+        <v>5.7586</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="G5" t="n">
-        <v>4.892</v>
+        <v>5.0275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9146</v>
+        <v>0.7506</v>
       </c>
       <c r="J5" t="n">
-        <v>4.892</v>
+        <v>5.0275</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>165</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8066</v>
+        <v>5.7781</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9035</v>
+        <v>4.6672</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7592</v>
+        <v>1.6745</v>
       </c>
       <c r="D6" t="n">
-        <v>1.608</v>
+        <v>1.5203</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9035</v>
+        <v>4.6672</v>
       </c>
       <c r="F6" t="n">
-        <v>4.385</v>
+        <v>4.1804</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5185</v>
+        <v>0.4868</v>
       </c>
       <c r="H6" t="n">
-        <v>9.573499999999999</v>
+        <v>9.2523</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1696</v>
+        <v>5.1949</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5185</v>
+        <v>0.4868</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>5.6881</v>
+        <v>5.681699999999999</v>
       </c>
       <c r="N6" t="n">
         <v>230</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2536</v>
+        <v>3.1844</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1673</v>
+        <v>1.1425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8569</v>
+        <v>0.8449</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2536</v>
+        <v>3.1844</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8848</v>
+        <v>2.8855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3688</v>
+        <v>0.2989</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6238</v>
+        <v>4.3906</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4968</v>
+        <v>2.4652</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3688</v>
+        <v>0.2989</v>
       </c>
       <c r="K7" t="n">
         <v>134</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8656</v>
+        <v>2.7641</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0419</v>
+        <v>3.0918</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0913</v>
+        <v>1.1092</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7605</v>
+        <v>0.8027</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0419</v>
+        <v>3.0918</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0747</v>
+        <v>3.1316</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0398</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2503</v>
+        <v>5.3148</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8351</v>
+        <v>2.9841</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0398</v>
       </c>
       <c r="K8" t="n">
         <v>148</v>
@@ -805,7 +805,7 @@
         <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8023</v>
+        <v>2.9443</v>
       </c>
       <c r="N8" t="n">
         <v>230</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8531</v>
+        <v>2.8576</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0236</v>
+        <v>1.0252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6746</v>
+        <v>0.696</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8531</v>
+        <v>2.8576</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5515</v>
+        <v>2.5987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3016</v>
+        <v>0.2589</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5241</v>
+        <v>3.314</v>
       </c>
       <c r="I9" t="n">
-        <v>1.903</v>
+        <v>1.8607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3016</v>
+        <v>0.2589</v>
       </c>
       <c r="K9" t="n">
         <v>148</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2046</v>
+        <v>2.1196</v>
       </c>
       <c r="N9" t="n">
         <v>230</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8141</v>
+        <v>2.6412</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0096</v>
+        <v>0.9476</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.5974</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8141</v>
+        <v>2.6412</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7506</v>
+        <v>2.6102</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0635</v>
+        <v>0.031</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7506</v>
+        <v>3.3573</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7957</v>
+        <v>1.885</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0635</v>
+        <v>0.031</v>
       </c>
       <c r="K10" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L10" t="n">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8592</v>
+        <v>1.916</v>
       </c>
       <c r="N10" t="n">
-        <v>295</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5801</v>
+        <v>2.5916</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9257</v>
+        <v>0.9298</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5503</v>
+        <v>0.5748</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5801</v>
+        <v>2.5916</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5332</v>
+        <v>1.6051</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0469</v>
+        <v>0.9865</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4638</v>
+        <v>1.6051</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8704</v>
+        <v>1.648</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0469</v>
+        <v>0.9865</v>
       </c>
       <c r="K11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9173</v>
+        <v>2.6345</v>
       </c>
       <c r="N11" t="n">
-        <v>215</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4456</v>
+        <v>2.4434</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8774</v>
+        <v>0.8766</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4891</v>
+        <v>0.5073</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4456</v>
+        <v>2.4434</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5966</v>
+        <v>2.6036</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.151</v>
+        <v>-0.1602</v>
       </c>
       <c r="H12" t="n">
-        <v>3.673</v>
+        <v>3.3325</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9834</v>
+        <v>1.8711</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.151</v>
+        <v>-0.1602</v>
       </c>
       <c r="K12" t="n">
         <v>134</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8324</v>
+        <v>1.7109</v>
       </c>
       <c r="N12" t="n">
         <v>215</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9314</v>
+        <v>1.9467</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6929</v>
+        <v>0.6984</v>
       </c>
       <c r="D13" t="n">
-        <v>0.255</v>
+        <v>0.281</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9314</v>
+        <v>1.9467</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0718</v>
+        <v>2.0849</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1404</v>
+        <v>-0.1382</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0718</v>
+        <v>2.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1252</v>
+        <v>2.1406</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1404</v>
+        <v>-0.1382</v>
       </c>
       <c r="K13" t="n">
         <v>118</v>
@@ -1035,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9848</v>
+        <v>2.0024</v>
       </c>
       <c r="N13" t="n">
         <v>157</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8393</v>
+        <v>1.8454</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6599</v>
+        <v>0.6621</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2131</v>
+        <v>0.2349</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8393</v>
+        <v>1.8454</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2473</v>
+        <v>1.2503</v>
       </c>
       <c r="G14" t="n">
-        <v>0.592</v>
+        <v>0.5951</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2473</v>
+        <v>1.2503</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2794</v>
+        <v>1.2837</v>
       </c>
       <c r="J14" t="n">
-        <v>0.592</v>
+        <v>0.5951</v>
       </c>
       <c r="K14" t="n">
         <v>142</v>
@@ -1081,7 +1081,7 @@
         <v>189</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8714</v>
+        <v>1.8788</v>
       </c>
       <c r="N14" t="n">
         <v>331</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8166</v>
+        <v>1.6024</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5749</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2028</v>
+        <v>0.1242</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8166</v>
+        <v>1.6024</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9343</v>
+        <v>1.7271</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1177</v>
+        <v>-0.1247</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9343</v>
+        <v>1.7271</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0445</v>
+        <v>0.9697</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1177</v>
+        <v>-0.1247</v>
       </c>
       <c r="K15" t="n">
         <v>134</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9268</v>
+        <v>0.845</v>
       </c>
       <c r="N15" t="n">
         <v>215</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5504</v>
+        <v>1.5377</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5562</v>
+        <v>0.5517</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5504</v>
+        <v>1.5377</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0473</v>
+        <v>1.4097</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5031</v>
+        <v>0.128</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0473</v>
+        <v>1.4097</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0743</v>
+        <v>1.4474</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5031</v>
+        <v>0.128</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="L16" t="n">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5774</v>
+        <v>1.5754</v>
       </c>
       <c r="N16" t="n">
-        <v>295</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4655</v>
+        <v>1.5141</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5258</v>
+        <v>0.5432</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0429</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4655</v>
+        <v>1.5141</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4128</v>
+        <v>0.9087</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0527</v>
+        <v>0.6054</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4128</v>
+        <v>0.9087</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4492</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0527</v>
+        <v>0.6054</v>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5019</v>
+        <v>1.5384</v>
       </c>
       <c r="N17" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3862</v>
+        <v>1.3111</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4973</v>
+        <v>0.4704</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0068</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3862</v>
+        <v>1.3111</v>
       </c>
       <c r="F18" t="n">
-        <v>2.259</v>
+        <v>2.1717</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8728</v>
+        <v>-0.8606</v>
       </c>
       <c r="H18" t="n">
-        <v>2.259</v>
+        <v>2.1717</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3172</v>
+        <v>2.2298</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8728</v>
+        <v>-0.8606</v>
       </c>
       <c r="K18" t="n">
         <v>118</v>
@@ -1265,7 +1265,7 @@
         <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4444</v>
+        <v>1.3692</v>
       </c>
       <c r="N18" t="n">
         <v>157</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0794</v>
+        <v>1.1037</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3873</v>
+        <v>0.396</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1328</v>
+        <v>-0.103</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0794</v>
+        <v>1.1037</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7107</v>
+        <v>0.7733</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3687</v>
+        <v>0.3304</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7107</v>
+        <v>0.7733</v>
       </c>
       <c r="I19" t="n">
-        <v>0.729</v>
+        <v>0.794</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3687</v>
+        <v>0.3304</v>
       </c>
       <c r="K19" t="n">
         <v>142</v>
@@ -1311,7 +1311,7 @@
         <v>189</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0977</v>
+        <v>1.1244</v>
       </c>
       <c r="N19" t="n">
         <v>331</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0363</v>
+        <v>0.9103</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3718</v>
+        <v>0.3266</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1525</v>
+        <v>-0.1911</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0363</v>
+        <v>0.9103</v>
       </c>
       <c r="F20" t="n">
-        <v>1.844</v>
+        <v>0.9103</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8077</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.844</v>
+        <v>0.9103</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8915</v>
+        <v>0.9103</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8077</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0838</v>
+        <v>0.9103</v>
       </c>
       <c r="N20" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9977</v>
+        <v>0.9008</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3579</v>
+        <v>0.3232</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.17</v>
+        <v>-0.1954</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9977</v>
+        <v>0.9008</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9977</v>
+        <v>1.6939</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.7931</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9977</v>
+        <v>1.6939</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9977</v>
+        <v>1.7391</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.7931</v>
       </c>
       <c r="K21" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9977</v>
+        <v>0.9460000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>114</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9928</v>
+        <v>0.8155</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3562</v>
+        <v>0.2926</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1723</v>
+        <v>-0.2343</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9928</v>
+        <v>0.8155</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8297</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1631</v>
+        <v>0.1255</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8297</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8297</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1631</v>
+        <v>0.1255</v>
       </c>
       <c r="K22" t="n">
         <v>118</v>
@@ -1449,7 +1449,7 @@
         <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9928</v>
+        <v>0.8154999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>180</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7251</v>
+        <v>0.7045</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2601</v>
+        <v>0.2528</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2941</v>
+        <v>-0.2849</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7251</v>
+        <v>0.7045</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7251</v>
+        <v>0.6978</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7251</v>
+        <v>0.6978</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7251</v>
+        <v>0.3918</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="K23" t="n">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7251</v>
+        <v>0.3985</v>
       </c>
       <c r="N23" t="n">
-        <v>114</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6582</v>
+        <v>0.6421</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2361</v>
+        <v>0.2304</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3246</v>
+        <v>-0.3133</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6582</v>
+        <v>0.6421</v>
       </c>
       <c r="F24" t="n">
-        <v>0.637</v>
+        <v>0.6421</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0212</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.637</v>
+        <v>0.6421</v>
       </c>
       <c r="I24" t="n">
-        <v>0.344</v>
+        <v>0.6421</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0212</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="L24" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3652</v>
+        <v>0.6421</v>
       </c>
       <c r="N24" t="n">
-        <v>230</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1596</v>
+        <v>0.1449</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4217</v>
+        <v>-0.4218</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4448</v>
+        <v>0.4039</v>
       </c>
       <c r="N25" t="n">
         <v>112</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3761</v>
+        <v>0.3173</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1349</v>
+        <v>0.1138</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.453</v>
+        <v>-0.4612</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3761</v>
+        <v>0.3173</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8789</v>
+        <v>0.7655</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5028</v>
+        <v>-0.4482</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8789</v>
+        <v>0.7655</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4746</v>
+        <v>0.4298</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5028</v>
+        <v>-0.4482</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>81</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0282</v>
+        <v>-0.01839999999999997</v>
       </c>
       <c r="N26" t="n">
         <v>215</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3531</v>
+        <v>0.2604</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1267</v>
+        <v>0.0934</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4635</v>
+        <v>-0.4872</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3531</v>
+        <v>0.2604</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8092</v>
+        <v>0.677</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4561</v>
+        <v>-0.4166</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8092</v>
+        <v>0.677</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8092</v>
+        <v>0.677</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4561</v>
+        <v>-0.4166</v>
       </c>
       <c r="K27" t="n">
         <v>118</v>
@@ -1679,7 +1679,7 @@
         <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3531</v>
+        <v>0.2604</v>
       </c>
       <c r="N27" t="n">
         <v>180</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1105</v>
+        <v>0.0862</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4839</v>
+        <v>-0.4964</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3081</v>
+        <v>0.2402</v>
       </c>
       <c r="N28" t="n">
         <v>114</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1615</v>
+        <v>0.0131</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0579</v>
+        <v>0.0047</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5507</v>
+        <v>-0.5998</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1615</v>
+        <v>0.0131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9029</v>
+        <v>0.7395</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7264</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9029</v>
+        <v>0.7395</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9262</v>
+        <v>0.7592</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7264</v>
       </c>
       <c r="K29" t="n">
         <v>118</v>
@@ -1771,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1848000000000001</v>
+        <v>0.03279999999999994</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1004</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0237</v>
+        <v>-0.036</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6543</v>
+        <v>-0.6515</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1004</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6956</v>
+        <v>-0.1522</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.0518</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6956</v>
+        <v>-0.1522</v>
       </c>
       <c r="K30" t="n">
         <v>118</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.04989999999999994</v>
+        <v>-0.1004</v>
       </c>
       <c r="N30" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0993</v>
+        <v>-0.1362</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0356</v>
+        <v>-0.0489</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6694</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0993</v>
+        <v>-0.1362</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0813</v>
+        <v>0.5395</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1806</v>
+        <v>-0.6757</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0813</v>
+        <v>0.5395</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0813</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1806</v>
+        <v>-0.6757</v>
       </c>
       <c r="K31" t="n">
         <v>118</v>
       </c>
       <c r="L31" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.09930000000000001</v>
+        <v>-0.1218</v>
       </c>
       <c r="N31" t="n">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3673</v>
+        <v>-0.3839</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1318</v>
+        <v>-0.1377</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7914</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3673</v>
+        <v>-0.3839</v>
       </c>
       <c r="F32" t="n">
-        <v>1.422</v>
+        <v>1.3722</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.7893</v>
+        <v>-1.7561</v>
       </c>
       <c r="H32" t="n">
-        <v>1.422</v>
+        <v>1.3722</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4586</v>
+        <v>1.4089</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.7893</v>
+        <v>-1.7561</v>
       </c>
       <c r="K32" t="n">
         <v>142</v>
@@ -1909,7 +1909,7 @@
         <v>189</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3307</v>
+        <v>-0.3472</v>
       </c>
       <c r="N32" t="n">
         <v>331</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5964</v>
+        <v>-0.5501</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.214</v>
+        <v>-0.1974</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5964</v>
+        <v>-0.5501</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.5718</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0301</v>
+        <v>0.0217</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.5718</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.5718</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0301</v>
+        <v>0.0217</v>
       </c>
       <c r="K33" t="n">
         <v>118</v>
@@ -1955,7 +1955,7 @@
         <v>62</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5963999999999999</v>
+        <v>-0.5500999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>180</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.318</v>
+        <v>-0.2991</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0277</v>
+        <v>-0.9855</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8864</v>
+        <v>-0.8336</v>
       </c>
       <c r="N34" t="n">
         <v>114</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3383</v>
+        <v>-0.3307</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0535</v>
+        <v>-1.0257</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9217</v>
       </c>
       <c r="N35" t="n">
         <v>112</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0237</v>
+        <v>-0.9556</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3673</v>
+        <v>-0.3428</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0902</v>
+        <v>-1.0411</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0237</v>
+        <v>-0.9556</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.498</v>
+        <v>-0.4685</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.4871</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.498</v>
+        <v>-0.4685</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.498</v>
+        <v>-0.4685</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.4871</v>
       </c>
       <c r="K36" t="n">
         <v>118</v>
@@ -2093,7 +2093,7 @@
         <v>62</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0237</v>
+        <v>-0.9556</v>
       </c>
       <c r="N36" t="n">
         <v>180</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4124</v>
+        <v>-0.388</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1475</v>
+        <v>-1.0985</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1495</v>
+        <v>-1.0816</v>
       </c>
       <c r="N37" t="n">
         <v>114</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4375</v>
+        <v>-0.4321</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1793</v>
+        <v>-1.1545</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2194</v>
+        <v>-1.2045</v>
       </c>
       <c r="N38" t="n">
         <v>112</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5472</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3322</v>
+        <v>-1.3005</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5552</v>
+        <v>-1.5251</v>
       </c>
       <c r="N39" t="n">
         <v>112</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5764</v>
+        <v>-0.5646</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3555</v>
+        <v>-1.3226</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6065</v>
+        <v>-1.5736</v>
       </c>
       <c r="N40" t="n">
         <v>112</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6355</v>
+        <v>-1.6292</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5868</v>
+        <v>-0.5845</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3687</v>
+        <v>-1.348</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6355</v>
+        <v>-1.6292</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9869</v>
+        <v>-1.9121</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3514</v>
+        <v>0.2829</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9869</v>
+        <v>-1.9121</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0729</v>
+        <v>-1.0736</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3514</v>
+        <v>0.2829</v>
       </c>
       <c r="K41" t="n">
         <v>148</v>
@@ -2323,7 +2323,7 @@
         <v>82</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.7215</v>
+        <v>-0.7907000000000002</v>
       </c>
       <c r="N41" t="n">
         <v>230</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1086</v>
+        <v>1.1124</v>
       </c>
       <c r="J2" t="n">
-        <v>26.6064</v>
+        <v>26.6976</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8578</v>
+        <v>0.8369</v>
       </c>
       <c r="J3" t="n">
-        <v>20.5872</v>
+        <v>20.0856</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7726</v>
       </c>
       <c r="J4" t="n">
-        <v>19.1496</v>
+        <v>18.5424</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4026</v>
+        <v>-0.3611</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.6624</v>
+        <v>-8.666399999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5034</v>
+        <v>-0.4635</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.0816</v>
+        <v>-11.124</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4952</v>
+        <v>0.4391</v>
       </c>
       <c r="J7" t="n">
-        <v>11.8848</v>
+        <v>10.5384</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0177</v>
+        <v>-0.0129</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4248</v>
+        <v>-0.3096</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1051</v>
+        <v>-0.0898</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5224</v>
+        <v>-2.1552</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2334</v>
+        <v>-0.2136</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.6016</v>
+        <v>-5.1264</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4551</v>
+        <v>-0.4498</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.9224</v>
+        <v>-10.7952</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.89</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6821</v>
+        <v>1.7129</v>
       </c>
       <c r="J12" t="n">
-        <v>35.3241</v>
+        <v>35.9709</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2888</v>
+        <v>1.3203</v>
       </c>
       <c r="J13" t="n">
-        <v>27.0648</v>
+        <v>27.7263</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9984</v>
+        <v>1.0017</v>
       </c>
       <c r="J14" t="n">
-        <v>20.9664</v>
+        <v>21.0357</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.43</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9626</v>
+        <v>0.963</v>
       </c>
       <c r="J15" t="n">
-        <v>20.2146</v>
+        <v>20.223</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0929</v>
+        <v>0.0655</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9509</v>
+        <v>1.3755</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1221</v>
+        <v>-0.1011</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5641</v>
+        <v>-2.1231</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2446</v>
+        <v>-0.2303</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.1366</v>
+        <v>-4.8363</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.63</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3694</v>
+        <v>-0.3605</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.7574</v>
+        <v>-7.5705</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.543</v>
+        <v>-0.5461</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.403</v>
+        <v>-11.4681</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6135</v>
+        <v>-0.6272</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.8835</v>
+        <v>-13.1712</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5683</v>
+        <v>0.5437</v>
       </c>
       <c r="J22" t="n">
-        <v>16.4807</v>
+        <v>15.7673</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0065</v>
+        <v>0.0038</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1885</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1075</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1175</v>
+        <v>-2.6361</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1075</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.1175</v>
+        <v>-2.6361</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4588</v>
+        <v>-0.4544</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.3052</v>
+        <v>-13.1776</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9354</v>
+        <v>0.9211</v>
       </c>
       <c r="J27" t="n">
-        <v>27.1266</v>
+        <v>26.7119</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8223</v>
+        <v>0.8064</v>
       </c>
       <c r="J28" t="n">
-        <v>23.8467</v>
+        <v>23.3856</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4133</v>
+        <v>0.3782</v>
       </c>
       <c r="J29" t="n">
-        <v>11.9857</v>
+        <v>10.9678</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2921</v>
+        <v>-0.2523</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.4709</v>
+        <v>-7.3167</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3482</v>
+        <v>-0.3069</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.0978</v>
+        <v>-8.9001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5785</v>
+        <v>0.5429</v>
       </c>
       <c r="J32" t="n">
-        <v>13.884</v>
+        <v>13.0296</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4528</v>
+        <v>0.3929</v>
       </c>
       <c r="J33" t="n">
-        <v>10.8672</v>
+        <v>9.429600000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3582</v>
+        <v>0.2995</v>
       </c>
       <c r="J34" t="n">
-        <v>8.5968</v>
+        <v>7.188</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1387</v>
+        <v>-0.1197</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.3288</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1505</v>
+        <v>-0.1312</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.612</v>
+        <v>-3.1488</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.15</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2939</v>
+        <v>0.2831</v>
       </c>
       <c r="J37" t="n">
-        <v>7.0536</v>
+        <v>6.7944</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1601</v>
+        <v>-0.1419</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.8424</v>
+        <v>-3.4056</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1707</v>
+        <v>-0.152</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.0968</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1915</v>
+        <v>-0.1722</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.596</v>
+        <v>-4.1328</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3462</v>
+        <v>-0.3307</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.3088</v>
+        <v>-7.9368</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J42" t="n">
-        <v>6.1886</v>
+        <v>4.9532</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.03</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1007</v>
+        <v>0.0743</v>
       </c>
       <c r="J43" t="n">
-        <v>2.9203</v>
+        <v>2.1547</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1007</v>
+        <v>0.0743</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9203</v>
+        <v>2.1547</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0985</v>
+        <v>-0.0818</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.8565</v>
+        <v>-2.3722</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1577</v>
+        <v>-0.1378</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.5733</v>
+        <v>-3.9962</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7699</v>
+        <v>0.7539</v>
       </c>
       <c r="J47" t="n">
-        <v>22.3271</v>
+        <v>21.8631</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3775</v>
+        <v>0.3375</v>
       </c>
       <c r="J48" t="n">
-        <v>10.9475</v>
+        <v>9.7875</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.327</v>
+        <v>0.2885</v>
       </c>
       <c r="J49" t="n">
-        <v>9.483000000000001</v>
+        <v>8.3665</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0114</v>
+        <v>-0.0076</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3306</v>
+        <v>-0.2204</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5797</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.8113</v>
+        <v>-15.6832</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0767</v>
+        <v>-0.0643</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.9175</v>
+        <v>-1.6075</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.91</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1265</v>
+        <v>-0.1103</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.1625</v>
+        <v>-2.7575</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1489</v>
+        <v>-0.1316</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.7225</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2208</v>
+        <v>-0.2014</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.52</v>
+        <v>-5.035</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2308</v>
+        <v>-0.2113</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.77</v>
+        <v>-5.2825</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9159</v>
+        <v>0.9011</v>
       </c>
       <c r="J57" t="n">
-        <v>22.8975</v>
+        <v>22.5275</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7306</v>
+        <v>0.7159</v>
       </c>
       <c r="J58" t="n">
-        <v>18.265</v>
+        <v>17.8975</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.25</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5954</v>
+        <v>0.5857</v>
       </c>
       <c r="J59" t="n">
-        <v>14.885</v>
+        <v>14.6425</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1381</v>
+        <v>0.1145</v>
       </c>
       <c r="J60" t="n">
-        <v>3.4525</v>
+        <v>2.8625</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4061</v>
+        <v>-0.3651</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.1525</v>
+        <v>-9.1275</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4331</v>
+        <v>0.3701</v>
       </c>
       <c r="J62" t="n">
-        <v>12.993</v>
+        <v>11.103</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.15</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2436</v>
+        <v>0.1954</v>
       </c>
       <c r="J63" t="n">
-        <v>7.308</v>
+        <v>5.862</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1773</v>
+        <v>0.1384</v>
       </c>
       <c r="J64" t="n">
-        <v>5.319</v>
+        <v>4.152</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1333</v>
+        <v>0.1016</v>
       </c>
       <c r="J65" t="n">
-        <v>3.999</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1208</v>
+        <v>-0.1021</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.624</v>
+        <v>-3.063</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5596</v>
+        <v>0.593</v>
       </c>
       <c r="J67" t="n">
-        <v>16.788</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2438</v>
+        <v>0.2284</v>
       </c>
       <c r="J68" t="n">
-        <v>7.314</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0577</v>
+        <v>-0.0453</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.731</v>
+        <v>-1.359</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2616</v>
+        <v>-0.2419</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.848</v>
+        <v>-7.257</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3833</v>
+        <v>-0.3715</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.499</v>
+        <v>-11.145</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0604</v>
       </c>
       <c r="J72" t="n">
-        <v>2.1996</v>
+        <v>1.5704</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0202</v>
+        <v>-0.015</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.5252</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.3962</v>
+        <v>-1.1206</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1738</v>
+        <v>-0.1542</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.5188</v>
+        <v>-4.0092</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2555</v>
+        <v>-0.2358</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.643</v>
+        <v>-6.1308</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.98</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5707</v>
+        <v>1.6039</v>
       </c>
       <c r="J77" t="n">
-        <v>40.8382</v>
+        <v>41.7014</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9796</v>
+        <v>0.9664</v>
       </c>
       <c r="J78" t="n">
-        <v>25.4696</v>
+        <v>25.1264</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.38</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7847</v>
+        <v>0.7696</v>
       </c>
       <c r="J79" t="n">
-        <v>20.4022</v>
+        <v>20.0096</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8101</v>
       </c>
       <c r="J80" t="n">
-        <v>-21.5046</v>
+        <v>-21.0626</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.52</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.2097</v>
+        <v>-1.2427</v>
       </c>
       <c r="J81" t="n">
-        <v>-31.4522</v>
+        <v>-32.3102</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.44</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8781</v>
+        <v>0.8626</v>
       </c>
       <c r="J82" t="n">
-        <v>22.8306</v>
+        <v>22.4276</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.38</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7923</v>
+        <v>0.7765</v>
       </c>
       <c r="J83" t="n">
-        <v>20.5998</v>
+        <v>20.189</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.31</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6893</v>
+        <v>0.6752</v>
       </c>
       <c r="J84" t="n">
-        <v>17.9218</v>
+        <v>17.5552</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3762</v>
+        <v>-0.3347</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.7812</v>
+        <v>-8.702199999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.86</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4788</v>
+        <v>-0.4383</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.4488</v>
+        <v>-11.3958</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0236</v>
+        <v>0.0181</v>
       </c>
       <c r="J87" t="n">
-        <v>0.6136</v>
+        <v>0.4706</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0612</v>
+        <v>-0.0502</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.5912</v>
+        <v>-1.3052</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2491</v>
+        <v>-0.23</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.4766</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2491</v>
+        <v>-0.23</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.4766</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2684</v>
+        <v>-0.2496</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.9784</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9665</v>
+        <v>0.9532</v>
       </c>
       <c r="J92" t="n">
-        <v>34.794</v>
+        <v>34.3152</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.48</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9387</v>
+        <v>0.9245</v>
       </c>
       <c r="J93" t="n">
-        <v>33.7932</v>
+        <v>33.282</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.24</v>
       </c>
       <c r="I94" t="n">
-        <v>0.585</v>
+        <v>0.5745</v>
       </c>
       <c r="J94" t="n">
-        <v>21.06</v>
+        <v>20.682</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3726</v>
+        <v>-0.3308</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.4136</v>
+        <v>-11.9088</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9012</v>
+        <v>-0.89</v>
       </c>
       <c r="J96" t="n">
-        <v>-32.4432</v>
+        <v>-32.04</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4122</v>
+        <v>0.3564</v>
       </c>
       <c r="J97" t="n">
-        <v>14.8392</v>
+        <v>12.8304</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0065</v>
+        <v>0.0038</v>
       </c>
       <c r="J98" t="n">
-        <v>0.234</v>
+        <v>0.1368</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1194</v>
+        <v>-0.102</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.2984</v>
+        <v>-3.672</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.207</v>
+        <v>-0.1866</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.452</v>
+        <v>-6.7176</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2573</v>
+        <v>-0.2375</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.2628</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.01</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0801</v>
+        <v>0.0608</v>
       </c>
       <c r="J102" t="n">
-        <v>1.7622</v>
+        <v>1.3376</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2069</v>
+        <v>-0.1892</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.5518</v>
+        <v>-4.1624</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2547</v>
+        <v>-0.2366</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.6034</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2643</v>
+        <v>-0.2462</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.8146</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.051</v>
+        <v>-6.6858</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2176</v>
+        <v>1.2148</v>
       </c>
       <c r="J107" t="n">
-        <v>26.7872</v>
+        <v>26.7256</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.56</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0124</v>
+        <v>1.0009</v>
       </c>
       <c r="J108" t="n">
-        <v>22.2728</v>
+        <v>22.0198</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.44</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8524</v>
+        <v>0.8396</v>
       </c>
       <c r="J109" t="n">
-        <v>18.7528</v>
+        <v>18.4712</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1476</v>
+        <v>0.1211</v>
       </c>
       <c r="J110" t="n">
-        <v>3.2472</v>
+        <v>2.6642</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.428</v>
+        <v>-0.3908</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.416</v>
+        <v>-8.5976</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.75</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2205</v>
+        <v>-0.199</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.7485</v>
+        <v>-3.383</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.53</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4409</v>
+        <v>-0.4391</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.4953</v>
+        <v>-7.4647</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.42</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5345</v>
+        <v>-0.5372</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.086499999999999</v>
+        <v>-9.132400000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.41</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5434</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.2378</v>
+        <v>-9.2973</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5523</v>
+        <v>-0.5567</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.389099999999999</v>
+        <v>-9.463900000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>2.29</v>
       </c>
       <c r="I117" t="n">
-        <v>1.8104</v>
+        <v>1.858</v>
       </c>
       <c r="J117" t="n">
-        <v>30.7768</v>
+        <v>31.586</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0028</v>
+        <v>1.0011</v>
       </c>
       <c r="J118" t="n">
-        <v>17.0476</v>
+        <v>17.0187</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.55</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="J119" t="n">
-        <v>16.4084</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.55</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="J120" t="n">
-        <v>16.4084</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.45</v>
       </c>
       <c r="I121" t="n">
-        <v>0.835</v>
+        <v>0.8314</v>
       </c>
       <c r="J121" t="n">
-        <v>14.195</v>
+        <v>14.1338</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1448</v>
+        <v>1.1597</v>
       </c>
       <c r="J122" t="n">
-        <v>33.1992</v>
+        <v>33.6313</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5397</v>
+        <v>0.5003</v>
       </c>
       <c r="J123" t="n">
-        <v>15.6513</v>
+        <v>14.5087</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2456</v>
+        <v>0.2122</v>
       </c>
       <c r="J124" t="n">
-        <v>7.1224</v>
+        <v>6.1538</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.306</v>
+        <v>-0.2646</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.874000000000001</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.652</v>
+        <v>-0.6173</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.908</v>
+        <v>-17.9017</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5059</v>
+        <v>0.4472</v>
       </c>
       <c r="J127" t="n">
-        <v>14.6711</v>
+        <v>12.9688</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4214</v>
+        <v>0.3643</v>
       </c>
       <c r="J128" t="n">
-        <v>12.2206</v>
+        <v>10.5647</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1099</v>
+        <v>-0.0925</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.1871</v>
+        <v>-2.6825</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.85</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.7913</v>
+        <v>-5.1939</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3551</v>
+        <v>-0.3407</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.2979</v>
+        <v>-9.8803</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0084</v>
+        <v>1.0103</v>
       </c>
       <c r="J132" t="n">
-        <v>25.21</v>
+        <v>25.2575</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9418</v>
+        <v>0.9341</v>
       </c>
       <c r="J133" t="n">
-        <v>23.545</v>
+        <v>23.3525</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6962</v>
+        <v>0.6731</v>
       </c>
       <c r="J134" t="n">
-        <v>17.405</v>
+        <v>16.8275</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I135" t="n">
-        <v>0.676</v>
+        <v>0.652</v>
       </c>
       <c r="J135" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.25</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6349</v>
+        <v>0.6092</v>
       </c>
       <c r="J136" t="n">
-        <v>15.8725</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2581</v>
+        <v>0.2149</v>
       </c>
       <c r="J137" t="n">
-        <v>6.4525</v>
+        <v>5.3725</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2135</v>
+        <v>0.1742</v>
       </c>
       <c r="J138" t="n">
-        <v>5.3375</v>
+        <v>4.355</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.71</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.012499999999999</v>
+        <v>-7.5975</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.67</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3572</v>
+        <v>-0.3426</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.93</v>
+        <v>-8.565</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4378</v>
+        <v>-0.4299</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.945</v>
+        <v>-10.7475</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.74</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4169</v>
+        <v>1.445</v>
       </c>
       <c r="J142" t="n">
-        <v>36.8394</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6883</v>
+        <v>0.6591</v>
       </c>
       <c r="J143" t="n">
-        <v>17.8958</v>
+        <v>17.1366</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4066</v>
+        <v>0.3729</v>
       </c>
       <c r="J144" t="n">
-        <v>10.5716</v>
+        <v>9.695399999999999</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1003</v>
+        <v>0.0799</v>
       </c>
       <c r="J145" t="n">
-        <v>2.6078</v>
+        <v>2.0774</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.301</v>
+        <v>-0.2619</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.826</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3562</v>
+        <v>0.3068</v>
       </c>
       <c r="J147" t="n">
-        <v>9.261200000000001</v>
+        <v>7.9768</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1861</v>
+        <v>0.149</v>
       </c>
       <c r="J148" t="n">
-        <v>4.8386</v>
+        <v>3.874</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2654</v>
+        <v>-0.2471</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.9004</v>
+        <v>-6.4246</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3494</v>
+        <v>-0.3342</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.0844</v>
+        <v>-8.6892</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4829</v>
+        <v>-0.4802</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.5554</v>
+        <v>-12.4852</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8207</v>
+        <v>0.7967</v>
       </c>
       <c r="J152" t="n">
-        <v>19.6968</v>
+        <v>19.1208</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.21</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5707</v>
+        <v>0.5352</v>
       </c>
       <c r="J153" t="n">
-        <v>13.6968</v>
+        <v>12.8448</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.438</v>
+        <v>0.4017</v>
       </c>
       <c r="J154" t="n">
-        <v>10.512</v>
+        <v>9.6408</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3156</v>
+        <v>0.2818</v>
       </c>
       <c r="J155" t="n">
-        <v>7.5744</v>
+        <v>6.7632</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.04</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1437</v>
+        <v>0.1196</v>
       </c>
       <c r="J156" t="n">
-        <v>3.4488</v>
+        <v>2.8704</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0858</v>
+        <v>-0.0728</v>
       </c>
       <c r="J157" t="n">
-        <v>-2.0592</v>
+        <v>-1.7472</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1346</v>
+        <v>-0.1188</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.2304</v>
+        <v>-2.8512</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.157</v>
+        <v>-0.1402</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.768</v>
+        <v>-3.3648</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.84</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1983</v>
+        <v>-0.1802</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.7592</v>
+        <v>-4.3248</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3778</v>
+        <v>-0.3645</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.0672</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6019</v>
+        <v>0.5313</v>
       </c>
       <c r="J162" t="n">
-        <v>13.8437</v>
+        <v>12.2199</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4373</v>
+        <v>0.375</v>
       </c>
       <c r="J163" t="n">
-        <v>10.0579</v>
+        <v>8.625</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.29</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3951</v>
+        <v>0.3359</v>
       </c>
       <c r="J164" t="n">
-        <v>9.087300000000001</v>
+        <v>7.7257</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.19</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2805</v>
+        <v>0.2319</v>
       </c>
       <c r="J165" t="n">
-        <v>6.4515</v>
+        <v>5.3337</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2556</v>
+        <v>0.2097</v>
       </c>
       <c r="J166" t="n">
-        <v>5.8788</v>
+        <v>4.8231</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.21</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3903</v>
+        <v>0.3919</v>
       </c>
       <c r="J167" t="n">
-        <v>8.976900000000001</v>
+        <v>9.0137</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1027</v>
+        <v>0.0885</v>
       </c>
       <c r="J168" t="n">
-        <v>2.3621</v>
+        <v>2.0355</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2955</v>
+        <v>-0.2776</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.7965</v>
+        <v>-6.3848</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3964</v>
+        <v>-0.3847</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.1172</v>
+        <v>-8.848100000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3964</v>
+        <v>-0.3847</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.1172</v>
+        <v>-8.848100000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5288</v>
+        <v>0.4693</v>
       </c>
       <c r="J172" t="n">
-        <v>15.3352</v>
+        <v>13.6097</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.378</v>
+        <v>0.3227</v>
       </c>
       <c r="J173" t="n">
-        <v>10.962</v>
+        <v>9.3583</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.12</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2876</v>
+        <v>0.2383</v>
       </c>
       <c r="J174" t="n">
-        <v>8.340400000000001</v>
+        <v>6.9107</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1925</v>
+        <v>-0.1719</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.5825</v>
+        <v>-4.9851</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3675</v>
+        <v>-0.3545</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.6575</v>
+        <v>-10.2805</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8006</v>
+        <v>0.7739</v>
       </c>
       <c r="J177" t="n">
-        <v>23.2174</v>
+        <v>22.4431</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6302</v>
+        <v>0.5934</v>
       </c>
       <c r="J178" t="n">
-        <v>18.2758</v>
+        <v>17.2086</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2998</v>
+        <v>0.2631</v>
       </c>
       <c r="J179" t="n">
-        <v>8.6942</v>
+        <v>7.6299</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1511</v>
+        <v>-0.1201</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.3819</v>
+        <v>-3.4829</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.511</v>
+        <v>-0.4696</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.819</v>
+        <v>-13.6184</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.3183</v>
+        <v>-0.3071</v>
       </c>
       <c r="J182" t="n">
-        <v>-6.6843</v>
+        <v>-6.4491</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.67</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3367</v>
+        <v>-0.3261</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.0707</v>
+        <v>-6.8481</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.62</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3798</v>
+        <v>-0.3701</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.9758</v>
+        <v>-7.7721</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.59</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4056</v>
+        <v>-0.3967</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.5176</v>
+        <v>-8.3307</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4143</v>
+        <v>-0.4057</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.7003</v>
+        <v>-8.5197</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.02</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6943</v>
+        <v>1.7416</v>
       </c>
       <c r="J187" t="n">
-        <v>35.5803</v>
+        <v>36.5736</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>2.02</v>
       </c>
       <c r="I188" t="n">
-        <v>1.6943</v>
+        <v>1.7416</v>
       </c>
       <c r="J188" t="n">
-        <v>35.5803</v>
+        <v>36.5736</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.3</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7155</v>
+        <v>0.698</v>
       </c>
       <c r="J189" t="n">
-        <v>15.0255</v>
+        <v>14.658</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4601</v>
+        <v>0.4296</v>
       </c>
       <c r="J190" t="n">
-        <v>9.662100000000001</v>
+        <v>9.021599999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.91</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3965</v>
+        <v>-0.3643</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.326499999999999</v>
+        <v>-7.6503</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3922</v>
+        <v>0.3904</v>
       </c>
       <c r="J192" t="n">
-        <v>7.4518</v>
+        <v>7.4176</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3927</v>
+        <v>-0.3853</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.4613</v>
+        <v>-7.3207</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.5</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4779</v>
+        <v>-0.4744</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.0801</v>
+        <v>-9.0136</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.522</v>
+        <v>-0.5226</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.917999999999999</v>
+        <v>-9.929399999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6548</v>
+        <v>-0.6756</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.4412</v>
+        <v>-12.8364</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.81</v>
       </c>
       <c r="I197" t="n">
-        <v>1.4459</v>
+        <v>1.4742</v>
       </c>
       <c r="J197" t="n">
-        <v>27.4721</v>
+        <v>28.0098</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.7</v>
       </c>
       <c r="I198" t="n">
-        <v>1.3127</v>
+        <v>1.3345</v>
       </c>
       <c r="J198" t="n">
-        <v>24.9413</v>
+        <v>25.3555</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.67</v>
       </c>
       <c r="I199" t="n">
-        <v>1.2759</v>
+        <v>1.2964</v>
       </c>
       <c r="J199" t="n">
-        <v>24.2421</v>
+        <v>24.6316</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.22</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5481</v>
+        <v>0.5212</v>
       </c>
       <c r="J200" t="n">
-        <v>10.4139</v>
+        <v>9.902799999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.154</v>
+        <v>0.1229</v>
       </c>
       <c r="J201" t="n">
-        <v>2.926</v>
+        <v>2.3351</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.72</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8601</v>
+        <v>0.7943</v>
       </c>
       <c r="J202" t="n">
-        <v>24.0828</v>
+        <v>22.2404</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0644</v>
+        <v>0.0462</v>
       </c>
       <c r="J203" t="n">
-        <v>1.8032</v>
+        <v>1.2936</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.02</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0444</v>
+        <v>0.0308</v>
       </c>
       <c r="J204" t="n">
-        <v>1.2432</v>
+        <v>0.8624000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.096</v>
+        <v>-0.0791</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.688</v>
+        <v>-2.2148</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1574</v>
+        <v>-0.1374</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.4072</v>
+        <v>-3.8472</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.393</v>
+        <v>0.3893</v>
       </c>
       <c r="J207" t="n">
-        <v>11.004</v>
+        <v>10.9004</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3669</v>
+        <v>0.3605</v>
       </c>
       <c r="J208" t="n">
-        <v>10.2732</v>
+        <v>10.094</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I209" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>2.2036</v>
+        <v>1.8256</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3006</v>
+        <v>-0.2827</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.4168</v>
+        <v>-7.9156</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3101</v>
+        <v>-0.2927</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.6828</v>
+        <v>-8.195600000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.84</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1574</v>
+        <v>-0.1382</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.148</v>
+        <v>-2.764</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.74</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2651</v>
+        <v>-0.252</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.302</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4287</v>
+        <v>-0.4216</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.574</v>
+        <v>-8.432</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4374</v>
+        <v>-0.4307</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.747999999999999</v>
+        <v>-8.614000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.35</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6135</v>
+        <v>-0.6272</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.27</v>
+        <v>-12.544</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3893</v>
+        <v>1.4135</v>
       </c>
       <c r="J217" t="n">
-        <v>27.786</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0979</v>
+        <v>1.112</v>
       </c>
       <c r="J218" t="n">
-        <v>21.958</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.5</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0715</v>
+        <v>1.0839</v>
       </c>
       <c r="J219" t="n">
-        <v>21.43</v>
+        <v>21.678</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5179</v>
+        <v>0.4893</v>
       </c>
       <c r="J220" t="n">
-        <v>10.358</v>
+        <v>9.786</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.02</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0354</v>
+        <v>0.0169</v>
       </c>
       <c r="J221" t="n">
-        <v>0.708</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.453</v>
+        <v>0.4117</v>
       </c>
       <c r="J222" t="n">
-        <v>15.855</v>
+        <v>14.4095</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.453</v>
+        <v>0.4117</v>
       </c>
       <c r="J223" t="n">
-        <v>15.855</v>
+        <v>14.4095</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0912</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J224" t="n">
-        <v>3.192</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0912</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>3.192</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1102</v>
+        <v>-0.0843</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.857</v>
+        <v>-2.9505</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6173</v>
+        <v>0.5579</v>
       </c>
       <c r="J227" t="n">
-        <v>21.6055</v>
+        <v>19.5265</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6173</v>
+        <v>0.5579</v>
       </c>
       <c r="J228" t="n">
-        <v>21.6055</v>
+        <v>19.5265</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.96</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0757</v>
+        <v>-0.0607</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.6495</v>
+        <v>-2.1245</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.83</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2259</v>
+        <v>-0.2055</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.9065</v>
+        <v>-7.1925</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2758</v>
+        <v>-0.257</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.653</v>
+        <v>-8.994999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.08</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2881</v>
+        <v>0.2481</v>
       </c>
       <c r="J232" t="n">
-        <v>8.354900000000001</v>
+        <v>7.1949</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1691</v>
+        <v>0.1375</v>
       </c>
       <c r="J233" t="n">
-        <v>4.9039</v>
+        <v>3.9875</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>0.059</v>
+        <v>0.0428</v>
       </c>
       <c r="J234" t="n">
-        <v>1.711</v>
+        <v>1.2412</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2301</v>
+        <v>-0.1934</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.6729</v>
+        <v>-5.6086</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.92</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2873</v>
+        <v>-0.2474</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.3317</v>
+        <v>-7.1746</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8028</v>
+        <v>0.7487</v>
       </c>
       <c r="J237" t="n">
-        <v>23.2812</v>
+        <v>21.7123</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.3</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5792</v>
+        <v>0.5193</v>
       </c>
       <c r="J238" t="n">
-        <v>16.7968</v>
+        <v>15.0597</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.95</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.6622</v>
+        <v>-2.1779</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1175</v>
+        <v>-0.099</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.4075</v>
+        <v>-2.871</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.326</v>
+        <v>-0.3102</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.454000000000001</v>
+        <v>-8.995799999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6531</v>
+        <v>0.5814</v>
       </c>
       <c r="J242" t="n">
-        <v>15.0213</v>
+        <v>13.3722</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5131</v>
       </c>
       <c r="J243" t="n">
-        <v>13.4136</v>
+        <v>11.8013</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.231</v>
+        <v>0.1877</v>
       </c>
       <c r="J244" t="n">
-        <v>5.313</v>
+        <v>4.3171</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.231</v>
+        <v>0.1877</v>
       </c>
       <c r="J245" t="n">
-        <v>5.313</v>
+        <v>4.3171</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.1</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1629</v>
+        <v>0.128</v>
       </c>
       <c r="J246" t="n">
-        <v>3.7467</v>
+        <v>2.944</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.174</v>
+        <v>0.158</v>
       </c>
       <c r="J247" t="n">
-        <v>4.002</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.06</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1565</v>
+        <v>0.1403</v>
       </c>
       <c r="J248" t="n">
-        <v>3.5995</v>
+        <v>3.2269</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2297</v>
+        <v>-0.2105</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.2831</v>
+        <v>-4.8415</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2686</v>
+        <v>-0.2498</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.1778</v>
+        <v>-5.7454</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4159</v>
+        <v>-0.4061</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.5657</v>
+        <v>-9.340299999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.17</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3893</v>
+        <v>0.3335</v>
       </c>
       <c r="J252" t="n">
-        <v>10.9004</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3533</v>
+        <v>0.2993</v>
       </c>
       <c r="J253" t="n">
-        <v>9.8924</v>
+        <v>8.3804</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0704</v>
+        <v>-0.057</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.9712</v>
+        <v>-1.596</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0838</v>
+        <v>-0.0689</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.3464</v>
+        <v>-1.9292</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.61</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4257</v>
+        <v>-0.4179</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.9196</v>
+        <v>-11.7012</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6708</v>
       </c>
       <c r="J257" t="n">
-        <v>19.7148</v>
+        <v>18.7824</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5713</v>
+        <v>0.5317</v>
       </c>
       <c r="J258" t="n">
-        <v>15.9964</v>
+        <v>14.8876</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.15</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4547</v>
+        <v>0.4131</v>
       </c>
       <c r="J259" t="n">
-        <v>12.7316</v>
+        <v>11.5668</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1087</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.0436</v>
+        <v>-2.3268</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8414</v>
+        <v>-0.8212</v>
       </c>
       <c r="J261" t="n">
-        <v>-23.5592</v>
+        <v>-22.9936</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.22</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4814</v>
+        <v>0.4237</v>
       </c>
       <c r="J262" t="n">
-        <v>13.9606</v>
+        <v>12.2873</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.01</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0503</v>
+        <v>0.0337</v>
       </c>
       <c r="J263" t="n">
-        <v>1.4587</v>
+        <v>0.9772999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.99</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0221</v>
+        <v>-0.0164</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.6409</v>
+        <v>-0.4756</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2865</v>
+        <v>-0.2678</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.3085</v>
+        <v>-7.7662</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2865</v>
+        <v>-0.2678</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.3085</v>
+        <v>-7.7662</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.42</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9819</v>
+        <v>0.976</v>
       </c>
       <c r="J267" t="n">
-        <v>28.4751</v>
+        <v>28.304</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.24</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6282</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>18.2178</v>
+        <v>17.2927</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5445</v>
+        <v>0.5108</v>
       </c>
       <c r="J269" t="n">
-        <v>15.7905</v>
+        <v>14.8132</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3344</v>
+        <v>0.3013</v>
       </c>
       <c r="J270" t="n">
-        <v>9.6976</v>
+        <v>8.7377</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.08</v>
       </c>
       <c r="I271" t="n">
-        <v>0.255</v>
+        <v>0.2242</v>
       </c>
       <c r="J271" t="n">
-        <v>7.395</v>
+        <v>6.5018</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.38</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5944</v>
+        <v>0.6262</v>
       </c>
       <c r="J272" t="n">
-        <v>15.4544</v>
+        <v>16.2812</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3759</v>
+        <v>0.3729</v>
       </c>
       <c r="J273" t="n">
-        <v>9.773400000000001</v>
+        <v>9.695399999999999</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.74</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3007</v>
+        <v>-0.2826</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.8182</v>
+        <v>-7.3476</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.71</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3287</v>
+        <v>-0.3122</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.546200000000001</v>
+        <v>-8.1172</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.45</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5573</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.4898</v>
+        <v>-14.716</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.64</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7743</v>
+        <v>0.7043</v>
       </c>
       <c r="J277" t="n">
-        <v>20.1318</v>
+        <v>18.3118</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5599</v>
+        <v>0.4896</v>
       </c>
       <c r="J278" t="n">
-        <v>14.5574</v>
+        <v>12.7296</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0109</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.2834</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1932</v>
+        <v>-0.1731</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.0232</v>
+        <v>-4.5006</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2352</v>
+        <v>-0.2157</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.1152</v>
+        <v>-5.6082</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2809</v>
+        <v>1.3016</v>
       </c>
       <c r="J282" t="n">
-        <v>30.7416</v>
+        <v>31.2384</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I283" t="n">
-        <v>0.785</v>
+        <v>0.758</v>
       </c>
       <c r="J283" t="n">
-        <v>18.84</v>
+        <v>18.192</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.25</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6602</v>
+        <v>0.6264</v>
       </c>
       <c r="J284" t="n">
-        <v>15.8448</v>
+        <v>15.0336</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4976</v>
+        <v>-0.4569</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.9424</v>
+        <v>-10.9656</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.7</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.8179</v>
       </c>
       <c r="J286" t="n">
-        <v>-20.0688</v>
+        <v>-19.6296</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7781</v>
+        <v>0.7335</v>
       </c>
       <c r="J287" t="n">
-        <v>18.6744</v>
+        <v>17.604</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.89</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1497</v>
+        <v>-0.1319</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.5928</v>
+        <v>-3.1656</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2321</v>
+        <v>-0.2124</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.5704</v>
+        <v>-5.0976</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.808</v>
+        <v>-5.3376</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4625</v>
+        <v>-0.4579</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.1</v>
+        <v>-10.9896</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.59</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2002</v>
+        <v>1.2154</v>
       </c>
       <c r="J292" t="n">
-        <v>30.005</v>
+        <v>30.385</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.068</v>
+        <v>1.0778</v>
       </c>
       <c r="J293" t="n">
-        <v>26.7</v>
+        <v>26.945</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9067</v>
+        <v>0.8951</v>
       </c>
       <c r="J294" t="n">
-        <v>22.6675</v>
+        <v>22.3775</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.35</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8317</v>
+        <v>0.8151</v>
       </c>
       <c r="J295" t="n">
-        <v>20.7925</v>
+        <v>20.3775</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6446</v>
+        <v>-0.6156</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.115</v>
+        <v>-15.39</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2092</v>
+        <v>0.1747</v>
       </c>
       <c r="J297" t="n">
-        <v>5.23</v>
+        <v>4.3675</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2601</v>
+        <v>-0.2436</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.5025</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.74</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2874</v>
+        <v>-0.2709</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.185</v>
+        <v>-6.7725</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.64</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3784</v>
+        <v>-0.3654</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3784</v>
+        <v>-0.3654</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.7</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3422</v>
+        <v>1.3637</v>
       </c>
       <c r="J302" t="n">
-        <v>30.8706</v>
+        <v>31.3651</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0956</v>
+        <v>1.1077</v>
       </c>
       <c r="J303" t="n">
-        <v>25.1988</v>
+        <v>25.4771</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.19</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5073</v>
+        <v>0.4772</v>
       </c>
       <c r="J304" t="n">
-        <v>11.6679</v>
+        <v>10.9756</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.16</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4388</v>
+        <v>0.4073</v>
       </c>
       <c r="J305" t="n">
-        <v>10.0924</v>
+        <v>9.367900000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1177</v>
+        <v>0.0936</v>
       </c>
       <c r="J306" t="n">
-        <v>2.7071</v>
+        <v>2.1528</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J307" t="n">
-        <v>-2.0562</v>
+        <v>-1.7434</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.88</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1494</v>
+        <v>-0.1338</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.4362</v>
+        <v>-3.0774</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2792</v>
+        <v>-0.2623</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.4216</v>
+        <v>-6.0329</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3345</v>
+        <v>-0.319</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.6935</v>
+        <v>-7.337</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3708</v>
+        <v>-0.3572</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.5284</v>
+        <v>-8.2156</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.6</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2132</v>
+        <v>1.2288</v>
       </c>
       <c r="J312" t="n">
-        <v>26.6904</v>
+        <v>27.0336</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9774</v>
+        <v>0.9742</v>
       </c>
       <c r="J313" t="n">
-        <v>21.5028</v>
+        <v>21.4324</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.41</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9351</v>
       </c>
       <c r="J314" t="n">
-        <v>20.746</v>
+        <v>20.5722</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.12</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3414</v>
+        <v>0.3094</v>
       </c>
       <c r="J315" t="n">
-        <v>7.5108</v>
+        <v>6.8068</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.06</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1791</v>
+        <v>0.151</v>
       </c>
       <c r="J316" t="n">
-        <v>3.9402</v>
+        <v>3.322</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0366</v>
+        <v>-0.0272</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.8052</v>
+        <v>-0.5984</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1171</v>
+        <v>-0.1025</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.5762</v>
+        <v>-2.255</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1844</v>
+        <v>-0.1679</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.0568</v>
+        <v>-3.6938</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.7</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3273</v>
+        <v>-0.3113</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.2006</v>
+        <v>-6.8486</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.453</v>
+        <v>-0.4466</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.965999999999999</v>
+        <v>-9.825200000000001</v>
       </c>
     </row>
   </sheetData>
